--- a/data/catalogo_db.xlsx
+++ b/data/catalogo_db.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jualo\Desktop\catalogo_epp\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2511D318-CCD9-4E3B-970C-A1980F4AEF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54A3B80D-CBC4-42B4-B1E0-0B953A6F97EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1201" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="905">
   <si>
     <t>SKU</t>
   </si>
@@ -85,9 +85,6 @@
     <t>ZAP-005</t>
   </si>
   <si>
-    <t>ZAPATO ECONOLINE</t>
-  </si>
-  <si>
     <t>PUNTA DE ACERO ANTICLAVO, ANTIDESLIZANTE TRABAJO DE HIDRUCARBUROS</t>
   </si>
   <si>
@@ -430,9 +427,6 @@
     <t>ROP-007</t>
   </si>
   <si>
-    <t>POLO 30AL1 PLOMO</t>
-  </si>
-  <si>
     <t>TELA DELGADA</t>
   </si>
   <si>
@@ -442,192 +436,66 @@
     <t>XL: 8.9, XXL: 9.9</t>
   </si>
   <si>
-    <t>ROP-010</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 AZUL MARINO</t>
-  </si>
-  <si>
     <t>XL: 9.9, XXL: 10.9</t>
   </si>
   <si>
-    <t>ROP-013</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 ROJO</t>
-  </si>
-  <si>
-    <t>ROP-016</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 NARANJA</t>
-  </si>
-  <si>
-    <t>ROP-019</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 AZULINO</t>
-  </si>
-  <si>
-    <t>ROP-022</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 VERDE JADE</t>
-  </si>
-  <si>
-    <t>ROP-028</t>
-  </si>
-  <si>
-    <t>POLO 30AL1 JERSEY PLOMO</t>
-  </si>
-  <si>
-    <t>TELA DELGADO JERSEY TALLAS COMPLETAS</t>
-  </si>
-  <si>
     <t>XL: 15.9,  XXL:16.9</t>
   </si>
   <si>
-    <t>ROP-031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POLO 30AL1 JERSEY AZUL MARINO </t>
-  </si>
-  <si>
-    <t>XL: 16.9,  XXL:18.9</t>
-  </si>
-  <si>
     <t>ROP-034</t>
   </si>
   <si>
-    <t xml:space="preserve">POLO 30AL1 JERSEY ROJO </t>
-  </si>
-  <si>
     <t>ROP-037</t>
   </si>
   <si>
-    <t xml:space="preserve">POLO 30AL1 JERSEY NARANJA </t>
-  </si>
-  <si>
     <t>ROP-040</t>
   </si>
   <si>
-    <t xml:space="preserve">POLO 30AL1 JERSEY AZULINO </t>
-  </si>
-  <si>
     <t>ROP-043</t>
   </si>
   <si>
-    <t xml:space="preserve">POLO 30AL1 JERSEY VERDE JADE </t>
-  </si>
-  <si>
     <t>ROP-049</t>
   </si>
   <si>
-    <t>POLO 20AL1 JERSEY PLOMO</t>
-  </si>
-  <si>
-    <t>TELA GRUESA JERSEY TALLAS COMPLETAS</t>
-  </si>
-  <si>
-    <t>XL: 18,  XXL:20</t>
-  </si>
-  <si>
     <t>ROP-052</t>
   </si>
   <si>
-    <t>POLO 20AL1 AZUL MARINO JERSEY</t>
-  </si>
-  <si>
-    <t>XL: 19,  XXL:21</t>
-  </si>
-  <si>
     <t>ROP-055</t>
   </si>
   <si>
-    <t>POLO 20AL1 ROJO JERSEY</t>
-  </si>
-  <si>
     <t>ROP-058</t>
   </si>
   <si>
-    <t>POLO 20AL1 NARANJA JERSEY</t>
-  </si>
-  <si>
     <t>ROP-061</t>
   </si>
   <si>
-    <t>POLO 20AL1 AZULINO JERSEY</t>
-  </si>
-  <si>
     <t>ROP-064</t>
   </si>
   <si>
-    <t>POLO 20AL1 VERDE JADE JERSEY</t>
-  </si>
-  <si>
     <t>ROP-046</t>
   </si>
   <si>
-    <t>POLO PIQUE CUELLO CAMISERO PLOMO</t>
-  </si>
-  <si>
     <t>XL: 32,  XXL:36</t>
   </si>
   <si>
-    <t>ROP-025</t>
-  </si>
-  <si>
-    <t>POLO 20AL1 PLOMO</t>
-  </si>
-  <si>
     <t>PLOMO TELA GRUESO</t>
   </si>
   <si>
     <t>ROP-067</t>
   </si>
   <si>
-    <t>CAMISA OXFORD AZUL ITALIANO NACIONAL</t>
-  </si>
-  <si>
     <t>S, M, L, XL, XXL</t>
   </si>
   <si>
     <t>ROP-068</t>
   </si>
   <si>
-    <t>CAMISA OXFORD CELESTE BB NACIONAL</t>
-  </si>
-  <si>
     <t>ROP-069</t>
   </si>
   <si>
-    <t>CAMISA OXFORD BLANCO NACIONAL</t>
-  </si>
-  <si>
     <t>ROP-070</t>
   </si>
   <si>
-    <t>CAMISA OXFORD NACIONAL PLOMO</t>
-  </si>
-  <si>
-    <t>BLUSA OXFORD AZUL ITALIANO NACIONAL</t>
-  </si>
-  <si>
-    <t>BLUSA OXFORD CELESTE BB NACIONAL</t>
-  </si>
-  <si>
-    <t>BLUSA OXFORD BLANCO NACIONAL</t>
-  </si>
-  <si>
-    <t>BLUSA OXFORD NACIONAL PLOMO</t>
-  </si>
-  <si>
-    <t>BLUSA OXFORD GREEN TEAM STEELPRO</t>
-  </si>
-  <si>
-    <t>CAMISA OXFORD GREEN TEAM STEELPRO</t>
-  </si>
-  <si>
     <t>M, L, XL, XXL</t>
   </si>
   <si>
@@ -730,9 +598,6 @@
     <t>CHA-020</t>
   </si>
   <si>
-    <t>CHALECO Η BEIGUE</t>
-  </si>
-  <si>
     <t>XXL:24</t>
   </si>
   <si>
@@ -892,21 +757,12 @@
     <t>MAMELUCO DRILL NARANJA</t>
   </si>
   <si>
-    <t>TRAJE TYVIC SEGPRO</t>
-  </si>
-  <si>
     <t>Filtra hasta en un 100% partículas de 3 micras</t>
   </si>
   <si>
-    <t>TRAJE TYVIC TECSEG</t>
-  </si>
-  <si>
     <t>45 GRAMOS</t>
   </si>
   <si>
-    <t>TRAJE TYVIC STEELPRO</t>
-  </si>
-  <si>
     <t>Confeccionado en tela no tejida de 50 gramos, compuesta de 3 capas:</t>
   </si>
   <si>
@@ -1870,12 +1726,6 @@
     <t>CORREA MODELO AMERICANO MEDIA LUNA GRANDE NACIONAL</t>
   </si>
   <si>
-    <t>CORREA MINERO DE NYLON PORTA LAMPARA NACIONAL</t>
-  </si>
-  <si>
-    <t>CORREA MINERO DE CUERO PORTA LAMPARA NACIONAL</t>
-  </si>
-  <si>
     <t>CINTA REFLECTIVA BI COLOR 3M</t>
   </si>
   <si>
@@ -2452,54 +2302,6 @@
     <t>ROP-009</t>
   </si>
   <si>
-    <t>ROP-011</t>
-  </si>
-  <si>
-    <t>ROP-012</t>
-  </si>
-  <si>
-    <t>ROP-014</t>
-  </si>
-  <si>
-    <t>ROP-015</t>
-  </si>
-  <si>
-    <t>ROP-017</t>
-  </si>
-  <si>
-    <t>ROP-018</t>
-  </si>
-  <si>
-    <t>ROP-020</t>
-  </si>
-  <si>
-    <t>ROP-021</t>
-  </si>
-  <si>
-    <t>ROP-023</t>
-  </si>
-  <si>
-    <t>ROP-024</t>
-  </si>
-  <si>
-    <t>ROP-026</t>
-  </si>
-  <si>
-    <t>ROP-027</t>
-  </si>
-  <si>
-    <t>ROP-029</t>
-  </si>
-  <si>
-    <t>ROP-030</t>
-  </si>
-  <si>
-    <t>ROP-032</t>
-  </si>
-  <si>
-    <t>ROP-033</t>
-  </si>
-  <si>
     <t>CHA-001</t>
   </si>
   <si>
@@ -2620,12 +2422,6 @@
     <t>ACC-030</t>
   </si>
   <si>
-    <t>ACC-031</t>
-  </si>
-  <si>
-    <t>ACC-032</t>
-  </si>
-  <si>
     <t>ACC-043</t>
   </si>
   <si>
@@ -2897,6 +2693,48 @@
   </si>
   <si>
     <t>SEN-023</t>
+  </si>
+  <si>
+    <t>ZAPATO ECONOLINE TECSEG</t>
+  </si>
+  <si>
+    <t>POLO 30 AL 1 PLOMO</t>
+  </si>
+  <si>
+    <t>POLO 30 AL 1 AZUL MARINO</t>
+  </si>
+  <si>
+    <t>POLO 30 AL 1 NARANJA</t>
+  </si>
+  <si>
+    <t>POLO 20 AL 1 PLOMO</t>
+  </si>
+  <si>
+    <t>POLO PIQUE CUELLO CAMISERO PLOMO MANGA LARGA</t>
+  </si>
+  <si>
+    <t>POLO PIQUE CUELLO CAMISERO PLOMO MANGA CORTA</t>
+  </si>
+  <si>
+    <t>XL: 29,  XXL:32</t>
+  </si>
+  <si>
+    <t>TRAJE TYVEK SEGPRO</t>
+  </si>
+  <si>
+    <t>TRAJE TYVEK TECSEG</t>
+  </si>
+  <si>
+    <t>TRAJE TYVEK STEELPRO</t>
+  </si>
+  <si>
+    <t>colores</t>
+  </si>
+  <si>
+    <t>xxx</t>
+  </si>
+  <si>
+    <t>CHALECO DRILL H BEIGE</t>
   </si>
 </sst>
 </file>
@@ -2946,10 +2784,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3252,18 +3089,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G396"/>
+  <dimension ref="A1:H370"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="34.6640625" customWidth="1"/>
+    <col min="2" max="2" width="52.77734375" customWidth="1"/>
     <col min="3" max="3" width="36.33203125" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" customWidth="1"/>
     <col min="5" max="5" width="7.88671875" customWidth="1"/>
     <col min="6" max="6" width="17.21875" customWidth="1"/>
     <col min="7" max="7" width="8.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3285,8 +3123,11 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H1" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -3306,7 +3147,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -3326,7 +3167,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>14</v>
       </c>
@@ -3346,7 +3187,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>17</v>
       </c>
@@ -3366,18 +3207,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>20</v>
       </c>
       <c r="B6" t="s">
+        <v>891</v>
+      </c>
+      <c r="C6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>22</v>
-      </c>
-      <c r="D6" t="s">
-        <v>23</v>
       </c>
       <c r="E6">
         <v>64</v>
@@ -3386,18 +3227,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
         <v>24</v>
       </c>
-      <c r="B7" t="s">
+      <c r="C7" t="s">
         <v>25</v>
       </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E7">
         <v>61.5</v>
@@ -3406,18 +3247,18 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" t="s">
         <v>27</v>
       </c>
-      <c r="B8" t="s">
-        <v>28</v>
-      </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E8">
         <v>66.5</v>
@@ -3426,18 +3267,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="s">
-        <v>31</v>
-      </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9">
         <v>68</v>
@@ -3446,18 +3287,18 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" t="s">
         <v>32</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
         <v>33</v>
-      </c>
-      <c r="C10" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" t="s">
-        <v>34</v>
       </c>
       <c r="E10">
         <v>63.5</v>
@@ -3466,18 +3307,18 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
         <v>35</v>
       </c>
-      <c r="B11" t="s">
+      <c r="C11" t="s">
         <v>36</v>
       </c>
-      <c r="C11" t="s">
-        <v>37</v>
-      </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11">
         <v>63.5</v>
@@ -3486,18 +3327,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
         <v>38</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" t="s">
         <v>39</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>40</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
       </c>
       <c r="E12">
         <v>119.9</v>
@@ -3506,18 +3347,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
         <v>42</v>
       </c>
-      <c r="B13" t="s">
-        <v>43</v>
-      </c>
       <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
         <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>41</v>
       </c>
       <c r="E13">
         <v>119.9</v>
@@ -3526,18 +3367,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B14" t="s">
         <v>44</v>
       </c>
-      <c r="B14" t="s">
-        <v>45</v>
-      </c>
       <c r="C14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" t="s">
         <v>40</v>
-      </c>
-      <c r="D14" t="s">
-        <v>41</v>
       </c>
       <c r="E14">
         <v>129.9</v>
@@ -3546,18 +3387,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" t="s">
         <v>46</v>
       </c>
-      <c r="B15" t="s">
-        <v>47</v>
-      </c>
       <c r="C15" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" t="s">
         <v>40</v>
-      </c>
-      <c r="D15" t="s">
-        <v>41</v>
       </c>
       <c r="E15">
         <v>129.9</v>
@@ -3566,18 +3407,18 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" t="s">
         <v>48</v>
       </c>
-      <c r="B16" t="s">
-        <v>49</v>
-      </c>
       <c r="C16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" t="s">
         <v>40</v>
-      </c>
-      <c r="D16" t="s">
-        <v>41</v>
       </c>
       <c r="E16">
         <v>119.9</v>
@@ -3588,16 +3429,16 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>49</v>
+      </c>
+      <c r="B17" t="s">
         <v>50</v>
       </c>
-      <c r="B17" t="s">
-        <v>51</v>
-      </c>
       <c r="C17" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" t="s">
         <v>40</v>
-      </c>
-      <c r="D17" t="s">
-        <v>41</v>
       </c>
       <c r="E17">
         <v>119.9</v>
@@ -3608,16 +3449,16 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
+        <v>51</v>
+      </c>
+      <c r="B18" t="s">
         <v>52</v>
       </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
       <c r="C18" t="s">
+        <v>39</v>
+      </c>
+      <c r="D18" t="s">
         <v>40</v>
-      </c>
-      <c r="D18" t="s">
-        <v>41</v>
       </c>
       <c r="E18">
         <v>119.9</v>
@@ -3628,13 +3469,13 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" t="s">
         <v>54</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
       </c>
       <c r="D19" t="s">
         <v>10</v>
@@ -3648,16 +3489,16 @@
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" t="s">
         <v>57</v>
       </c>
-      <c r="B20" t="s">
+      <c r="C20" t="s">
         <v>58</v>
       </c>
-      <c r="C20" t="s">
-        <v>59</v>
-      </c>
       <c r="D20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20">
         <v>169.9</v>
@@ -3668,16 +3509,16 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21" t="s">
         <v>60</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C21" t="s">
         <v>61</v>
       </c>
-      <c r="C21" t="s">
-        <v>62</v>
-      </c>
       <c r="D21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21">
         <v>205</v>
@@ -3688,16 +3529,16 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" t="s">
         <v>63</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>64</v>
       </c>
-      <c r="C22" t="s">
-        <v>65</v>
-      </c>
       <c r="D22" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E22">
         <v>290</v>
@@ -3708,16 +3549,16 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
+        <v>65</v>
+      </c>
+      <c r="B23" t="s">
         <v>66</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>67</v>
       </c>
-      <c r="C23" t="s">
-        <v>68</v>
-      </c>
       <c r="D23" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E23">
         <v>340</v>
@@ -3728,16 +3569,16 @@
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" t="s">
         <v>69</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>70</v>
       </c>
-      <c r="C24" t="s">
-        <v>71</v>
-      </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E24">
         <v>350</v>
@@ -3748,16 +3589,16 @@
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
+        <v>71</v>
+      </c>
+      <c r="B25" t="s">
         <v>72</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>73</v>
       </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
       <c r="D25" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E25">
         <v>270</v>
@@ -3769,16 +3610,16 @@
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
+        <v>74</v>
+      </c>
+      <c r="B26" t="s">
         <v>75</v>
       </c>
-      <c r="B26" t="s">
-        <v>76</v>
-      </c>
       <c r="C26" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E26">
         <v>78</v>
@@ -3789,16 +3630,16 @@
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
+        <v>76</v>
+      </c>
+      <c r="B27" t="s">
         <v>77</v>
       </c>
-      <c r="B27" t="s">
+      <c r="C27" t="s">
         <v>78</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>79</v>
-      </c>
-      <c r="D27" t="s">
-        <v>80</v>
       </c>
       <c r="E27">
         <v>81</v>
@@ -3809,16 +3650,16 @@
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
+        <v>80</v>
+      </c>
+      <c r="B28" t="s">
         <v>81</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>82</v>
       </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
       <c r="D28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E28">
         <v>98</v>
@@ -3829,22 +3670,22 @@
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
+        <v>83</v>
+      </c>
+      <c r="B29" t="s">
         <v>84</v>
       </c>
-      <c r="B29" t="s">
+      <c r="C29" t="s">
         <v>85</v>
       </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
       <c r="D29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E29">
         <v>26</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="G29">
         <v>28</v>
@@ -3852,22 +3693,22 @@
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" t="s">
         <v>88</v>
       </c>
-      <c r="B30" t="s">
+      <c r="C30" t="s">
         <v>89</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>90</v>
-      </c>
-      <c r="D30" t="s">
-        <v>91</v>
       </c>
       <c r="E30">
         <v>36</v>
       </c>
       <c r="F30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G30">
         <v>29</v>
@@ -3875,22 +3716,22 @@
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
+        <v>92</v>
+      </c>
+      <c r="B31" t="s">
         <v>93</v>
       </c>
-      <c r="B31" t="s">
-        <v>94</v>
-      </c>
       <c r="C31" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E31">
         <v>23.5</v>
       </c>
       <c r="F31" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G31">
         <v>30</v>
@@ -3898,22 +3739,22 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
         <v>96</v>
       </c>
-      <c r="B32" t="s">
-        <v>97</v>
-      </c>
       <c r="C32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32">
         <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G32">
         <v>31</v>
@@ -3921,19 +3762,19 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
+        <v>98</v>
+      </c>
+      <c r="B33" t="s">
         <v>99</v>
       </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
       <c r="D33" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E33">
         <v>78</v>
       </c>
       <c r="F33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G33">
         <v>32</v>
@@ -3941,19 +3782,19 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
         <v>102</v>
       </c>
-      <c r="B34" t="s">
-        <v>103</v>
-      </c>
       <c r="D34" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E34">
         <v>118</v>
       </c>
       <c r="F34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G34">
         <v>33</v>
@@ -3961,19 +3802,19 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
+        <v>104</v>
+      </c>
+      <c r="B35" t="s">
         <v>105</v>
       </c>
-      <c r="B35" t="s">
-        <v>106</v>
-      </c>
       <c r="D35" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E35">
         <v>228</v>
       </c>
       <c r="F35" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G35">
         <v>34</v>
@@ -3981,13 +3822,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
         <v>108</v>
       </c>
-      <c r="B36" t="s">
-        <v>109</v>
-      </c>
       <c r="D36" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E36">
         <v>177</v>
@@ -3998,13 +3839,13 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>804</v>
+        <v>754</v>
       </c>
       <c r="B37" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" t="s">
         <v>110</v>
-      </c>
-      <c r="D37" t="s">
-        <v>111</v>
       </c>
       <c r="E37">
         <v>28</v>
@@ -4015,13 +3856,13 @@
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
+        <v>111</v>
+      </c>
+      <c r="B38" t="s">
         <v>112</v>
       </c>
-      <c r="B38" t="s">
+      <c r="C38" t="s">
         <v>113</v>
-      </c>
-      <c r="C38" t="s">
-        <v>114</v>
       </c>
       <c r="E38">
         <v>149</v>
@@ -4032,13 +3873,13 @@
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" t="s">
         <v>115</v>
       </c>
-      <c r="B39" t="s">
+      <c r="C39" t="s">
         <v>116</v>
-      </c>
-      <c r="C39" t="s">
-        <v>117</v>
       </c>
       <c r="E39">
         <v>149</v>
@@ -4049,13 +3890,13 @@
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
+        <v>117</v>
+      </c>
+      <c r="B40" t="s">
         <v>118</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>119</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
       </c>
       <c r="E40">
         <v>18</v>
@@ -4066,10 +3907,10 @@
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
+        <v>120</v>
+      </c>
+      <c r="B41" t="s">
         <v>121</v>
-      </c>
-      <c r="B41" t="s">
-        <v>122</v>
       </c>
       <c r="E41">
         <v>20</v>
@@ -4080,16 +3921,16 @@
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
+        <v>122</v>
+      </c>
+      <c r="B42" t="s">
         <v>123</v>
-      </c>
-      <c r="B42" t="s">
-        <v>124</v>
       </c>
       <c r="E42">
         <v>39.9</v>
       </c>
       <c r="F42" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G42">
         <v>41</v>
@@ -4097,22 +3938,22 @@
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
+        <v>125</v>
+      </c>
+      <c r="B43" t="s">
         <v>126</v>
       </c>
-      <c r="B43" t="s">
+      <c r="C43" t="s">
         <v>127</v>
       </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>128</v>
-      </c>
-      <c r="D43" t="s">
-        <v>129</v>
       </c>
       <c r="E43">
         <v>16</v>
       </c>
       <c r="F43" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G43">
         <v>42</v>
@@ -4120,22 +3961,22 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>805</v>
+        <v>755</v>
       </c>
       <c r="B44" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C44" t="s">
+        <v>127</v>
+      </c>
+      <c r="D44" t="s">
         <v>128</v>
-      </c>
-      <c r="D44" t="s">
-        <v>129</v>
       </c>
       <c r="E44">
         <v>16</v>
       </c>
       <c r="F44" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G44">
         <v>43</v>
@@ -4143,22 +3984,22 @@
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C45" t="s">
+        <v>127</v>
+      </c>
+      <c r="D45" t="s">
         <v>128</v>
-      </c>
-      <c r="D45" t="s">
-        <v>129</v>
       </c>
       <c r="E45">
         <v>16</v>
       </c>
       <c r="F45" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G45">
         <v>44</v>
@@ -4166,22 +4007,22 @@
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>806</v>
+        <v>756</v>
       </c>
       <c r="B46" t="s">
+        <v>892</v>
+      </c>
+      <c r="C46" t="s">
+        <v>135</v>
+      </c>
+      <c r="D46" t="s">
         <v>136</v>
-      </c>
-      <c r="C46" t="s">
-        <v>137</v>
-      </c>
-      <c r="D46" t="s">
-        <v>138</v>
       </c>
       <c r="E46">
         <v>7.9</v>
       </c>
       <c r="F46" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="G46">
         <v>45</v>
@@ -4189,22 +4030,22 @@
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B47" t="s">
-        <v>141</v>
+        <v>893</v>
       </c>
       <c r="C47" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E47">
         <v>8.9</v>
       </c>
       <c r="F47" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G47">
         <v>46</v>
@@ -4212,5837 +4053,5303 @@
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>807</v>
+        <v>757</v>
       </c>
       <c r="B48" t="s">
-        <v>144</v>
+        <v>894</v>
       </c>
       <c r="C48" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E48">
         <v>8.9</v>
       </c>
       <c r="F48" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="G48">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s">
-        <v>146</v>
-      </c>
-      <c r="C49" t="s">
-        <v>137</v>
+        <v>896</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E49">
-        <v>8.9</v>
+        <v>29</v>
       </c>
       <c r="F49" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G49">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+        <v>51</v>
+      </c>
+      <c r="H49" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>808</v>
+        <v>758</v>
       </c>
       <c r="B50" t="s">
-        <v>148</v>
-      </c>
-      <c r="C50" t="s">
-        <v>137</v>
+        <v>897</v>
       </c>
       <c r="D50" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E50">
-        <v>8.9</v>
+        <v>25</v>
       </c>
       <c r="F50" t="s">
-        <v>142</v>
+        <v>898</v>
       </c>
       <c r="G50">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+        <v>370</v>
+      </c>
+      <c r="H50" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>809</v>
+        <v>759</v>
       </c>
       <c r="B51" t="s">
-        <v>150</v>
+        <v>895</v>
       </c>
       <c r="C51" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E51">
-        <v>8.9</v>
+        <v>14.9</v>
       </c>
       <c r="F51" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="G51">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>140</v>
+        <v>760</v>
       </c>
       <c r="B52" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="C52" t="s">
-        <v>153</v>
-      </c>
-      <c r="D52" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="E52">
-        <v>14.9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>154</v>
+        <v>5.5</v>
       </c>
       <c r="G52">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>810</v>
+        <v>159</v>
       </c>
       <c r="B53" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C53" t="s">
-        <v>153</v>
-      </c>
-      <c r="D53" t="s">
-        <v>138</v>
+        <v>161</v>
       </c>
       <c r="E53">
-        <v>15.9</v>
-      </c>
-      <c r="F53" t="s">
-        <v>157</v>
+        <v>5.5</v>
       </c>
       <c r="G53">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>811</v>
+        <v>162</v>
       </c>
       <c r="B54" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="C54" t="s">
-        <v>153</v>
-      </c>
-      <c r="D54" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="E54">
-        <v>15.9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>157</v>
+        <v>6.5</v>
       </c>
       <c r="G54">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="B55" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C55" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" t="s">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="E55">
-        <v>15.9</v>
-      </c>
-      <c r="F55" t="s">
-        <v>157</v>
+        <v>6.5</v>
       </c>
       <c r="G55">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>812</v>
+        <v>167</v>
       </c>
       <c r="B56" t="s">
-        <v>163</v>
-      </c>
-      <c r="C56" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E56">
-        <v>15.9</v>
+        <v>37</v>
       </c>
       <c r="F56" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="G56">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>813</v>
+        <v>169</v>
       </c>
       <c r="B57" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="C57" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="D57" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E57">
-        <v>15.9</v>
+        <v>16</v>
       </c>
       <c r="F57" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="G57">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>145</v>
+        <v>761</v>
       </c>
       <c r="B58" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="C58" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D58" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E58">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F58" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="G58">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>814</v>
+        <v>172</v>
       </c>
       <c r="B59" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="C59" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D59" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E59">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F59" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G59">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>815</v>
+        <v>762</v>
       </c>
       <c r="B60" t="s">
+        <v>183</v>
+      </c>
+      <c r="C60" t="s">
         <v>174</v>
       </c>
-      <c r="C60" t="s">
-        <v>168</v>
-      </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E60">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F60" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="G60">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>147</v>
+        <v>176</v>
       </c>
       <c r="B61" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C61" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E61">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G61">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>816</v>
+        <v>763</v>
       </c>
       <c r="B62" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="C62" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D62" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E62">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F62" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="G62">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>817</v>
+        <v>179</v>
       </c>
       <c r="B63" t="s">
-        <v>180</v>
+        <v>904</v>
       </c>
       <c r="C63" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D63" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E63">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F63" t="s">
-        <v>172</v>
+        <v>192</v>
       </c>
       <c r="G63">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>149</v>
+        <v>764</v>
       </c>
       <c r="B64" t="s">
-        <v>182</v>
+        <v>194</v>
+      </c>
+      <c r="C64" t="s">
+        <v>195</v>
       </c>
       <c r="D64" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E64">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F64" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G64">
-        <v>51</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>818</v>
+        <v>182</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="C65" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E65">
-        <v>14.9</v>
+        <v>16</v>
       </c>
       <c r="F65" t="s">
-        <v>154</v>
+        <v>198</v>
       </c>
       <c r="G65">
-        <v>45</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>819</v>
+        <v>765</v>
       </c>
       <c r="B66" t="s">
-        <v>188</v>
+        <v>199</v>
+      </c>
+      <c r="C66" t="s">
+        <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="E66">
-        <v>29.9</v>
+        <v>16</v>
+      </c>
+      <c r="F66" t="s">
+        <v>200</v>
       </c>
       <c r="G66">
-        <v>52</v>
+        <v>74</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B67" t="s">
-        <v>191</v>
-      </c>
-      <c r="D67" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="E67">
-        <v>29.9</v>
+        <v>49.9</v>
       </c>
       <c r="G67">
-        <v>53</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>820</v>
+        <v>766</v>
       </c>
       <c r="B68" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D68" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="E68">
-        <v>29.9</v>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F68" t="s">
+        <v>203</v>
       </c>
       <c r="G68">
-        <v>54</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>821</v>
+        <v>188</v>
       </c>
       <c r="B69" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="D69" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="E69">
-        <v>29.9</v>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F69" t="s">
+        <v>203</v>
       </c>
       <c r="G69">
-        <v>55</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>151</v>
+        <v>767</v>
       </c>
       <c r="B70" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="D70" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="E70">
-        <v>29.9</v>
+        <v>109.9</v>
+      </c>
+      <c r="F70" t="s">
+        <v>203</v>
       </c>
       <c r="G70">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>822</v>
+        <v>191</v>
       </c>
       <c r="B71" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="D71" t="s">
-        <v>189</v>
+        <v>128</v>
       </c>
       <c r="E71">
-        <v>29.9</v>
+        <v>79.900000000000006</v>
+      </c>
+      <c r="F71" t="s">
+        <v>207</v>
       </c>
       <c r="G71">
-        <v>57</v>
+        <v>79</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>823</v>
+        <v>768</v>
       </c>
       <c r="B72" t="s">
-        <v>198</v>
-      </c>
-      <c r="D72" t="s">
-        <v>189</v>
+        <v>208</v>
       </c>
       <c r="E72">
-        <v>29.9</v>
+        <v>36</v>
       </c>
       <c r="G72">
-        <v>58</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>155</v>
+        <v>193</v>
       </c>
       <c r="B73" t="s">
-        <v>199</v>
-      </c>
-      <c r="D73" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="E73">
-        <v>29.9</v>
+        <v>33</v>
       </c>
       <c r="G73">
-        <v>59</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>824</v>
+        <v>140</v>
       </c>
       <c r="B74" t="s">
-        <v>200</v>
+        <v>210</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="E74">
-        <v>35.9</v>
+        <v>135</v>
+      </c>
+      <c r="F74" t="s">
+        <v>211</v>
       </c>
       <c r="G74">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>825</v>
+        <v>769</v>
       </c>
       <c r="B75" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="D75" t="s">
-        <v>202</v>
+        <v>128</v>
       </c>
       <c r="E75">
-        <v>32.9</v>
+        <v>135</v>
+      </c>
+      <c r="F75" t="s">
+        <v>211</v>
       </c>
       <c r="G75">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>826</v>
+        <v>770</v>
       </c>
       <c r="B76" t="s">
-        <v>204</v>
-      </c>
-      <c r="C76" t="s">
-        <v>205</v>
+        <v>819</v>
+      </c>
+      <c r="D76" t="s">
+        <v>128</v>
       </c>
       <c r="E76">
-        <v>5.5</v>
+        <v>75</v>
+      </c>
+      <c r="F76" t="s">
+        <v>207</v>
       </c>
       <c r="G76">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="B77" t="s">
-        <v>207</v>
-      </c>
-      <c r="C77" t="s">
-        <v>205</v>
+        <v>213</v>
+      </c>
+      <c r="D77" t="s">
+        <v>128</v>
       </c>
       <c r="E77">
-        <v>5.5</v>
+        <v>95</v>
+      </c>
+      <c r="F77" t="s">
+        <v>214</v>
       </c>
       <c r="G77">
-        <v>63</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>206</v>
+        <v>771</v>
       </c>
       <c r="B78" t="s">
-        <v>209</v>
-      </c>
-      <c r="C78" t="s">
-        <v>210</v>
+        <v>215</v>
+      </c>
+      <c r="D78" t="s">
+        <v>128</v>
       </c>
       <c r="E78">
-        <v>6.5</v>
+        <v>79.900000000000006</v>
+      </c>
+      <c r="F78" t="s">
+        <v>216</v>
       </c>
       <c r="G78">
-        <v>62</v>
+        <v>84</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>208</v>
+        <v>772</v>
       </c>
       <c r="B79" t="s">
-        <v>212</v>
-      </c>
-      <c r="C79" t="s">
-        <v>210</v>
+        <v>217</v>
+      </c>
+      <c r="D79" t="s">
+        <v>128</v>
       </c>
       <c r="E79">
-        <v>6.5</v>
+        <v>105</v>
+      </c>
+      <c r="F79" t="s">
+        <v>218</v>
       </c>
       <c r="G79">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>211</v>
+        <v>142</v>
       </c>
       <c r="B80" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="D80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E80">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="F80" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="G80">
-        <v>64</v>
+        <v>86</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>213</v>
+        <v>773</v>
       </c>
       <c r="B81" t="s">
-        <v>217</v>
-      </c>
-      <c r="C81" t="s">
-        <v>218</v>
+        <v>820</v>
       </c>
       <c r="D81" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E81">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="F81" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="G81">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>827</v>
+        <v>774</v>
       </c>
       <c r="B82" t="s">
-        <v>221</v>
-      </c>
-      <c r="C82" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D82" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E82">
-        <v>16</v>
+        <v>79.900000000000006</v>
       </c>
       <c r="F82" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="G82">
-        <v>66</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>216</v>
+        <v>143</v>
       </c>
       <c r="B83" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C83" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D83" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E83">
-        <v>16</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="F83" t="s">
-        <v>225</v>
+        <v>187</v>
       </c>
       <c r="G83">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>828</v>
+        <v>775</v>
       </c>
       <c r="B84" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="C84" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D84" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E84">
-        <v>16</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="F84" t="s">
-        <v>228</v>
+        <v>187</v>
       </c>
       <c r="G84">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>220</v>
+        <v>776</v>
       </c>
       <c r="B85" t="s">
-        <v>230</v>
-      </c>
-      <c r="C85" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="D85" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E85">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="F85" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="G85">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>829</v>
+        <v>150</v>
       </c>
       <c r="B86" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="C86" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="D86" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="F86" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="G86">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>223</v>
+        <v>777</v>
       </c>
       <c r="B87" t="s">
-        <v>236</v>
-      </c>
-      <c r="C87" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="D87" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="F87" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="G87">
-        <v>71</v>
+        <v>93</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>830</v>
+        <v>778</v>
       </c>
       <c r="B88" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="C88" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D88" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E88">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F88" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="G88">
-        <v>72</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>226</v>
+        <v>144</v>
       </c>
       <c r="B89" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="C89" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="D89" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E89">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="F89" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="G89">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>831</v>
+        <v>779</v>
       </c>
       <c r="B90" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="C90" t="s">
-        <v>240</v>
-      </c>
-      <c r="D90" t="s">
-        <v>129</v>
+        <v>236</v>
       </c>
       <c r="E90">
         <v>16</v>
       </c>
-      <c r="F90" t="s">
-        <v>245</v>
-      </c>
       <c r="G90">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>229</v>
+        <v>780</v>
       </c>
       <c r="B91" t="s">
-        <v>246</v>
+        <v>237</v>
+      </c>
+      <c r="C91" t="s">
+        <v>238</v>
+      </c>
+      <c r="D91" t="s">
+        <v>239</v>
       </c>
       <c r="E91">
-        <v>49.9</v>
+        <v>17</v>
       </c>
       <c r="G91">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>832</v>
+        <v>145</v>
       </c>
       <c r="B92" t="s">
-        <v>247</v>
+        <v>240</v>
+      </c>
+      <c r="C92" t="s">
+        <v>241</v>
       </c>
       <c r="D92" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E92">
-        <v>69.900000000000006</v>
-      </c>
-      <c r="F92" t="s">
-        <v>248</v>
+        <v>29.9</v>
       </c>
       <c r="G92">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>232</v>
+        <v>781</v>
       </c>
       <c r="B93" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="D93" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E93">
-        <v>69.900000000000006</v>
+        <v>36</v>
       </c>
       <c r="F93" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G93">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>833</v>
+        <v>782</v>
       </c>
       <c r="B94" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D94" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E94">
-        <v>109.9</v>
+        <v>36</v>
       </c>
       <c r="F94" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="G94">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>235</v>
+        <v>146</v>
       </c>
       <c r="B95" t="s">
-        <v>251</v>
+        <v>899</v>
+      </c>
+      <c r="C95" t="s">
+        <v>245</v>
       </c>
       <c r="D95" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E95">
-        <v>79.900000000000006</v>
-      </c>
-      <c r="F95" t="s">
-        <v>252</v>
+        <v>5</v>
       </c>
       <c r="G95">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>834</v>
+        <v>783</v>
       </c>
       <c r="B96" t="s">
-        <v>253</v>
+        <v>900</v>
+      </c>
+      <c r="C96" t="s">
+        <v>246</v>
+      </c>
+      <c r="D96" t="s">
+        <v>158</v>
       </c>
       <c r="E96">
-        <v>36</v>
+        <v>5.5</v>
       </c>
       <c r="G96">
-        <v>1000</v>
+        <v>102</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>238</v>
+        <v>784</v>
       </c>
       <c r="B97" t="s">
-        <v>254</v>
+        <v>901</v>
+      </c>
+      <c r="C97" t="s">
+        <v>247</v>
+      </c>
+      <c r="D97" t="s">
+        <v>154</v>
       </c>
       <c r="E97">
-        <v>33</v>
+        <v>5.5</v>
       </c>
       <c r="G97">
-        <v>1001</v>
+        <v>103</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="B98" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="D98" t="s">
-        <v>129</v>
+        <v>239</v>
       </c>
       <c r="E98">
-        <v>135</v>
-      </c>
-      <c r="F98" t="s">
-        <v>256</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G98">
-        <v>80</v>
+        <v>104</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>835</v>
+        <v>785</v>
       </c>
       <c r="B99" t="s">
-        <v>257</v>
+        <v>249</v>
+      </c>
+      <c r="C99" t="s">
+        <v>250</v>
       </c>
       <c r="D99" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E99">
-        <v>135</v>
-      </c>
-      <c r="F99" t="s">
-        <v>256</v>
+        <v>19</v>
       </c>
       <c r="G99">
-        <v>81</v>
+        <v>105</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>836</v>
+        <v>786</v>
       </c>
       <c r="B100" t="s">
-        <v>887</v>
+        <v>251</v>
+      </c>
+      <c r="C100" t="s">
+        <v>252</v>
       </c>
       <c r="D100" t="s">
-        <v>129</v>
+        <v>158</v>
       </c>
       <c r="E100">
-        <v>75</v>
-      </c>
-      <c r="F100" t="s">
-        <v>252</v>
+        <v>19</v>
       </c>
       <c r="G100">
-        <v>82</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B101" t="s">
-        <v>258</v>
+        <v>253</v>
+      </c>
+      <c r="C101" t="s">
+        <v>254</v>
       </c>
       <c r="D101" t="s">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="E101">
-        <v>95</v>
-      </c>
-      <c r="F101" t="s">
-        <v>259</v>
+        <v>25</v>
       </c>
       <c r="G101">
-        <v>83</v>
+        <v>107</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>837</v>
+        <v>787</v>
       </c>
       <c r="B102" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="D102" t="s">
-        <v>129</v>
+        <v>256</v>
       </c>
       <c r="E102">
-        <v>79.900000000000006</v>
+        <v>32</v>
       </c>
       <c r="F102" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="G102">
-        <v>84</v>
+        <v>108</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>838</v>
+        <v>788</v>
       </c>
       <c r="B103" t="s">
-        <v>262</v>
-      </c>
-      <c r="D103" t="s">
-        <v>129</v>
+        <v>821</v>
+      </c>
+      <c r="C103" t="s">
+        <v>259</v>
       </c>
       <c r="E103">
-        <v>105</v>
-      </c>
-      <c r="F103" t="s">
-        <v>263</v>
+        <v>2.5</v>
       </c>
       <c r="G103">
-        <v>85</v>
+        <v>109</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B104" t="s">
-        <v>264</v>
-      </c>
-      <c r="D104" t="s">
-        <v>129</v>
+        <v>258</v>
+      </c>
+      <c r="C104" t="s">
+        <v>259</v>
       </c>
       <c r="E104">
-        <v>105</v>
-      </c>
-      <c r="F104" t="s">
-        <v>263</v>
+        <v>2.5</v>
       </c>
       <c r="G104">
-        <v>86</v>
+        <v>110</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>839</v>
+        <v>789</v>
       </c>
       <c r="B105" t="s">
-        <v>888</v>
-      </c>
-      <c r="D105" t="s">
-        <v>129</v>
+        <v>260</v>
+      </c>
+      <c r="C105" t="s">
+        <v>259</v>
       </c>
       <c r="E105">
-        <v>75</v>
-      </c>
-      <c r="F105" t="s">
-        <v>252</v>
+        <v>2.5</v>
       </c>
       <c r="G105">
-        <v>87</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>840</v>
+        <v>790</v>
       </c>
       <c r="B106" t="s">
-        <v>265</v>
-      </c>
-      <c r="D106" t="s">
-        <v>129</v>
+        <v>261</v>
+      </c>
+      <c r="C106" t="s">
+        <v>259</v>
       </c>
       <c r="E106">
-        <v>79.900000000000006</v>
-      </c>
-      <c r="F106" t="s">
-        <v>261</v>
+        <v>2.5</v>
       </c>
       <c r="G106">
-        <v>88</v>
+        <v>112</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B107" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="C107" t="s">
-        <v>267</v>
-      </c>
-      <c r="D107" t="s">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="E107">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="F107" t="s">
-        <v>231</v>
+        <v>2.5</v>
       </c>
       <c r="G107">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>841</v>
+        <v>155</v>
       </c>
       <c r="B108" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="C108" t="s">
-        <v>267</v>
-      </c>
-      <c r="D108" t="s">
-        <v>129</v>
+        <v>259</v>
       </c>
       <c r="E108">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="F108" t="s">
-        <v>231</v>
+        <v>2.5</v>
       </c>
       <c r="G108">
-        <v>90</v>
+        <v>114</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>842</v>
+        <v>156</v>
       </c>
       <c r="B109" t="s">
-        <v>269</v>
-      </c>
-      <c r="D109" t="s">
-        <v>129</v>
+        <v>264</v>
+      </c>
+      <c r="C109" t="s">
+        <v>259</v>
       </c>
       <c r="E109">
-        <v>33</v>
-      </c>
-      <c r="F109" t="s">
-        <v>270</v>
+        <v>2.5</v>
       </c>
       <c r="G109">
-        <v>91</v>
+        <v>115</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="B110" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C110" t="s">
-        <v>272</v>
-      </c>
-      <c r="D110" t="s">
-        <v>129</v>
+        <v>266</v>
       </c>
       <c r="E110">
-        <v>36</v>
-      </c>
-      <c r="F110" t="s">
-        <v>273</v>
+        <v>4.5</v>
       </c>
       <c r="G110">
-        <v>92</v>
+        <v>116</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="B111" t="s">
-        <v>274</v>
-      </c>
-      <c r="D111" t="s">
-        <v>129</v>
+        <v>267</v>
+      </c>
+      <c r="C111" t="s">
+        <v>266</v>
       </c>
       <c r="E111">
-        <v>35</v>
-      </c>
-      <c r="F111" t="s">
-        <v>275</v>
+        <v>4.5</v>
       </c>
       <c r="G111">
-        <v>93</v>
+        <v>117</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>844</v>
+        <v>791</v>
       </c>
       <c r="B112" t="s">
+        <v>275</v>
+      </c>
+      <c r="C112" t="s">
         <v>276</v>
       </c>
-      <c r="C112" t="s">
-        <v>272</v>
-      </c>
-      <c r="D112" t="s">
-        <v>129</v>
-      </c>
       <c r="E112">
-        <v>26</v>
-      </c>
-      <c r="F112" t="s">
-        <v>277</v>
+        <v>7.9</v>
       </c>
       <c r="G112">
-        <v>94</v>
+        <v>122</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>166</v>
+        <v>792</v>
       </c>
       <c r="B113" t="s">
         <v>278</v>
       </c>
       <c r="C113" t="s">
-        <v>272</v>
-      </c>
-      <c r="D113" t="s">
-        <v>129</v>
+        <v>279</v>
       </c>
       <c r="E113">
-        <v>26</v>
-      </c>
-      <c r="F113" t="s">
-        <v>279</v>
+        <v>16</v>
       </c>
       <c r="G113">
-        <v>95</v>
+        <v>123</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>845</v>
+        <v>274</v>
       </c>
       <c r="B114" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="C114" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="E114">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="G114">
-        <v>96</v>
+        <v>124</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>846</v>
+        <v>277</v>
       </c>
       <c r="B115" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C115" t="s">
-        <v>283</v>
-      </c>
-      <c r="D115" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E115">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G115">
-        <v>97</v>
+        <v>125</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>170</v>
+        <v>280</v>
       </c>
       <c r="B116" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C116" t="s">
-        <v>286</v>
-      </c>
-      <c r="D116" t="s">
-        <v>129</v>
+        <v>288</v>
       </c>
       <c r="E116">
-        <v>29.9</v>
+        <v>48</v>
       </c>
       <c r="G116">
-        <v>98</v>
+        <v>126</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>847</v>
+        <v>283</v>
       </c>
       <c r="B117" t="s">
-        <v>287</v>
-      </c>
-      <c r="D117" t="s">
-        <v>129</v>
+        <v>290</v>
+      </c>
+      <c r="C117" t="s">
+        <v>276</v>
       </c>
       <c r="E117">
-        <v>36</v>
-      </c>
-      <c r="F117" t="s">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="G117">
-        <v>99</v>
+        <v>127</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>848</v>
+        <v>286</v>
       </c>
       <c r="B118" t="s">
-        <v>289</v>
-      </c>
-      <c r="D118" t="s">
-        <v>129</v>
+        <v>292</v>
+      </c>
+      <c r="C118" t="s">
+        <v>293</v>
       </c>
       <c r="E118">
-        <v>36</v>
-      </c>
-      <c r="F118" t="s">
-        <v>288</v>
+        <v>27</v>
       </c>
       <c r="G118">
-        <v>100</v>
+        <v>128</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>173</v>
+        <v>289</v>
       </c>
       <c r="B119" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C119" t="s">
-        <v>291</v>
-      </c>
-      <c r="D119" t="s">
-        <v>202</v>
+        <v>296</v>
       </c>
       <c r="E119">
-        <v>5</v>
+        <v>58</v>
       </c>
       <c r="G119">
-        <v>101</v>
+        <v>129</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>849</v>
+        <v>291</v>
       </c>
       <c r="B120" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="C120" t="s">
-        <v>293</v>
-      </c>
-      <c r="D120" t="s">
-        <v>202</v>
+        <v>299</v>
       </c>
       <c r="E120">
-        <v>5.5</v>
+        <v>85</v>
       </c>
       <c r="G120">
-        <v>102</v>
+        <v>130</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>850</v>
+        <v>294</v>
       </c>
       <c r="B121" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="C121" t="s">
-        <v>295</v>
-      </c>
-      <c r="D121" t="s">
-        <v>189</v>
+        <v>301</v>
       </c>
       <c r="E121">
-        <v>5.5</v>
+        <v>89</v>
       </c>
       <c r="G121">
-        <v>103</v>
+        <v>131</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>175</v>
+        <v>297</v>
       </c>
       <c r="B122" t="s">
-        <v>296</v>
-      </c>
-      <c r="D122" t="s">
-        <v>284</v>
+        <v>302</v>
+      </c>
+      <c r="C122" t="s">
+        <v>303</v>
       </c>
       <c r="E122">
-        <v>19.899999999999999</v>
+        <v>45</v>
       </c>
       <c r="G122">
-        <v>104</v>
+        <v>132</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>851</v>
+        <v>836</v>
       </c>
       <c r="B123" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="C123" t="s">
-        <v>298</v>
-      </c>
-      <c r="D123" t="s">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="E123">
-        <v>19</v>
+        <v>8.9</v>
       </c>
       <c r="G123">
-        <v>105</v>
+        <v>118</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>852</v>
+        <v>837</v>
       </c>
       <c r="B124" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="C124" t="s">
-        <v>300</v>
-      </c>
-      <c r="D124" t="s">
-        <v>202</v>
+        <v>271</v>
       </c>
       <c r="E124">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G124">
-        <v>106</v>
+        <v>119</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>177</v>
+        <v>838</v>
       </c>
       <c r="B125" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="C125" t="s">
-        <v>302</v>
-      </c>
-      <c r="D125" t="s">
-        <v>189</v>
+        <v>271</v>
       </c>
       <c r="E125">
-        <v>25</v>
+        <v>9.9</v>
       </c>
       <c r="G125">
-        <v>107</v>
+        <v>120</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>853</v>
+        <v>839</v>
       </c>
       <c r="B126" t="s">
-        <v>303</v>
-      </c>
-      <c r="D126" t="s">
-        <v>304</v>
+        <v>273</v>
+      </c>
+      <c r="C126" t="s">
+        <v>271</v>
       </c>
       <c r="E126">
-        <v>32</v>
-      </c>
-      <c r="F126" t="s">
-        <v>305</v>
+        <v>11</v>
       </c>
       <c r="G126">
-        <v>108</v>
+        <v>121</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>854</v>
+        <v>840</v>
       </c>
       <c r="B127" t="s">
-        <v>889</v>
-      </c>
-      <c r="C127" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E127">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="G127">
-        <v>109</v>
+        <v>133</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>179</v>
+        <v>841</v>
       </c>
       <c r="B128" t="s">
-        <v>306</v>
-      </c>
-      <c r="C128" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E128">
-        <v>2.5</v>
+        <v>19</v>
       </c>
       <c r="G128">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>855</v>
+        <v>842</v>
       </c>
       <c r="B129" t="s">
-        <v>308</v>
-      </c>
-      <c r="C129" t="s">
         <v>307</v>
       </c>
       <c r="E129">
-        <v>2.5</v>
+        <v>23</v>
       </c>
       <c r="G129">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>856</v>
+        <v>843</v>
       </c>
       <c r="B130" t="s">
         <v>309</v>
       </c>
-      <c r="C130" t="s">
-        <v>307</v>
-      </c>
       <c r="E130">
-        <v>2.5</v>
+        <v>95</v>
       </c>
       <c r="G130">
-        <v>112</v>
+        <v>136</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>187</v>
+        <v>844</v>
       </c>
       <c r="B131" t="s">
-        <v>310</v>
-      </c>
-      <c r="C131" t="s">
-        <v>307</v>
+        <v>620</v>
       </c>
       <c r="E131">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="G131">
-        <v>113</v>
+        <v>285</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>190</v>
+        <v>845</v>
       </c>
       <c r="B132" t="s">
-        <v>311</v>
-      </c>
-      <c r="C132" t="s">
-        <v>307</v>
+        <v>622</v>
       </c>
       <c r="E132">
-        <v>2.5</v>
+        <v>12</v>
       </c>
       <c r="G132">
-        <v>114</v>
+        <v>286</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>192</v>
+        <v>846</v>
       </c>
       <c r="B133" t="s">
-        <v>312</v>
-      </c>
-      <c r="C133" t="s">
-        <v>307</v>
+        <v>623</v>
       </c>
       <c r="E133">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="G133">
-        <v>115</v>
+        <v>287</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
-        <v>194</v>
+        <v>306</v>
       </c>
       <c r="B134" t="s">
-        <v>313</v>
-      </c>
-      <c r="C134" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="E134">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G134">
-        <v>116</v>
+        <v>137</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
-        <v>903</v>
+        <v>308</v>
       </c>
       <c r="B135" t="s">
-        <v>315</v>
-      </c>
-      <c r="C135" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E135">
-        <v>4.5</v>
+        <v>2</v>
       </c>
       <c r="G135">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
-        <v>857</v>
+        <v>793</v>
       </c>
       <c r="B136" t="s">
-        <v>323</v>
-      </c>
-      <c r="C136" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E136">
-        <v>7.9</v>
+        <v>17</v>
       </c>
       <c r="G136">
-        <v>122</v>
+        <v>139</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
-        <v>858</v>
+        <v>794</v>
       </c>
       <c r="B137" t="s">
-        <v>326</v>
-      </c>
-      <c r="C137" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="E137">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="G137">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B138" t="s">
-        <v>329</v>
-      </c>
-      <c r="C138" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="E138">
-        <v>15.5</v>
+        <v>1</v>
       </c>
       <c r="G138">
-        <v>124</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="B139" t="s">
-        <v>332</v>
-      </c>
-      <c r="C139" t="s">
-        <v>333</v>
+        <v>318</v>
       </c>
       <c r="E139">
-        <v>16</v>
+        <v>1.9</v>
       </c>
       <c r="G139">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="B140" t="s">
-        <v>335</v>
+        <v>320</v>
       </c>
       <c r="C140" t="s">
-        <v>336</v>
+        <v>321</v>
+      </c>
+      <c r="D140" t="s">
+        <v>322</v>
       </c>
       <c r="E140">
-        <v>48</v>
+        <v>26.9</v>
       </c>
       <c r="G140">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
       <c r="B141" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="C141" t="s">
         <v>324</v>
       </c>
+      <c r="D141" t="s">
+        <v>256</v>
+      </c>
       <c r="E141">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="G141">
-        <v>127</v>
+        <v>144</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
       <c r="B142" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="C142" t="s">
-        <v>341</v>
+        <v>327</v>
+      </c>
+      <c r="D142" t="s">
+        <v>256</v>
       </c>
       <c r="E142">
-        <v>27</v>
+        <v>36.5</v>
       </c>
       <c r="G142">
-        <v>128</v>
+        <v>145</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B143" t="s">
-        <v>343</v>
-      </c>
-      <c r="C143" t="s">
-        <v>344</v>
+        <v>329</v>
+      </c>
+      <c r="D143" t="s">
+        <v>136</v>
       </c>
       <c r="E143">
-        <v>58</v>
+        <v>41.5</v>
       </c>
       <c r="G143">
-        <v>129</v>
+        <v>146</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="B144" t="s">
-        <v>346</v>
-      </c>
-      <c r="C144" t="s">
-        <v>347</v>
+        <v>331</v>
+      </c>
+      <c r="D144" t="s">
+        <v>136</v>
       </c>
       <c r="E144">
-        <v>85</v>
+        <v>41.5</v>
       </c>
       <c r="G144">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="B145" t="s">
-        <v>348</v>
-      </c>
-      <c r="C145" t="s">
-        <v>349</v>
+        <v>333</v>
+      </c>
+      <c r="D145" t="s">
+        <v>256</v>
       </c>
       <c r="E145">
-        <v>89</v>
+        <v>37.5</v>
       </c>
       <c r="G145">
-        <v>131</v>
+        <v>148</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="B146" t="s">
-        <v>350</v>
-      </c>
-      <c r="C146" t="s">
-        <v>351</v>
+        <v>335</v>
+      </c>
+      <c r="D146" t="s">
+        <v>256</v>
       </c>
       <c r="E146">
-        <v>45</v>
+        <v>37.5</v>
       </c>
       <c r="G146">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>904</v>
-      </c>
-      <c r="B147" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="D147" s="2"/>
-      <c r="E147" s="2">
-        <v>8.9</v>
-      </c>
-      <c r="F147" s="2"/>
-      <c r="G147" s="2">
-        <v>118</v>
+        <v>338</v>
+      </c>
+      <c r="B147" t="s">
+        <v>337</v>
+      </c>
+      <c r="D147" t="s">
+        <v>256</v>
+      </c>
+      <c r="E147">
+        <v>36</v>
+      </c>
+      <c r="G147">
+        <v>150</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>905</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D148" s="2"/>
-      <c r="E148" s="2">
-        <v>15</v>
-      </c>
-      <c r="F148" s="2"/>
-      <c r="G148" s="2">
-        <v>119</v>
+        <v>341</v>
+      </c>
+      <c r="B148" t="s">
+        <v>339</v>
+      </c>
+      <c r="D148" t="s">
+        <v>340</v>
+      </c>
+      <c r="E148">
+        <v>36</v>
+      </c>
+      <c r="G148">
+        <v>151</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
-        <v>906</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D149" s="2"/>
-      <c r="E149" s="2">
-        <v>9.9</v>
-      </c>
-      <c r="F149" s="2"/>
-      <c r="G149" s="2">
-        <v>120</v>
+        <v>343</v>
+      </c>
+      <c r="B149" t="s">
+        <v>342</v>
+      </c>
+      <c r="D149" t="s">
+        <v>340</v>
+      </c>
+      <c r="E149">
+        <v>42</v>
+      </c>
+      <c r="G149">
+        <v>152</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
-        <v>907</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="C150" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="D150" s="2"/>
-      <c r="E150" s="2">
-        <v>11</v>
-      </c>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2">
-        <v>121</v>
+        <v>345</v>
+      </c>
+      <c r="B150" t="s">
+        <v>344</v>
+      </c>
+      <c r="D150" t="s">
+        <v>256</v>
+      </c>
+      <c r="E150">
+        <v>42</v>
+      </c>
+      <c r="G150">
+        <v>153</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>908</v>
+        <v>348</v>
       </c>
       <c r="B151" t="s">
-        <v>352</v>
+        <v>346</v>
+      </c>
+      <c r="D151" t="s">
+        <v>347</v>
       </c>
       <c r="E151">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="G151">
-        <v>133</v>
+        <v>154</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>909</v>
+        <v>350</v>
       </c>
       <c r="B152" t="s">
-        <v>353</v>
+        <v>349</v>
+      </c>
+      <c r="D152" t="s">
+        <v>256</v>
       </c>
       <c r="E152">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="G152">
-        <v>134</v>
+        <v>155</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>910</v>
+        <v>352</v>
       </c>
       <c r="B153" t="s">
-        <v>355</v>
+        <v>351</v>
+      </c>
+      <c r="D153" t="s">
+        <v>340</v>
       </c>
       <c r="E153">
-        <v>23</v>
+        <v>324</v>
       </c>
       <c r="G153">
-        <v>135</v>
+        <v>156</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>911</v>
+        <v>355</v>
       </c>
       <c r="B154" t="s">
+        <v>353</v>
+      </c>
+      <c r="D154" t="s">
+        <v>354</v>
+      </c>
+      <c r="E154">
+        <v>37.5</v>
+      </c>
+      <c r="G154">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" t="s">
+        <v>358</v>
+      </c>
+      <c r="B155" t="s">
+        <v>356</v>
+      </c>
+      <c r="D155" t="s">
         <v>357</v>
       </c>
-      <c r="E154">
-        <v>95</v>
-      </c>
-      <c r="G154">
+      <c r="E155">
+        <v>42</v>
+      </c>
+      <c r="G155">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" t="s">
+        <v>360</v>
+      </c>
+      <c r="B156" t="s">
+        <v>359</v>
+      </c>
+      <c r="D156" t="s">
         <v>136</v>
       </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A155" s="2" t="s">
-        <v>912</v>
-      </c>
-      <c r="B155" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C155" s="2"/>
-      <c r="D155" s="2"/>
-      <c r="E155" s="2">
-        <v>12</v>
-      </c>
-      <c r="F155" s="2"/>
-      <c r="G155" s="2">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A156" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C156" s="2"/>
-      <c r="D156" s="2"/>
-      <c r="E156" s="2">
-        <v>12</v>
-      </c>
-      <c r="F156" s="2"/>
-      <c r="G156" s="2">
-        <v>286</v>
+      <c r="E156">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="G156">
+        <v>159</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A157" s="2" t="s">
-        <v>914</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="C157" s="2"/>
-      <c r="D157" s="2"/>
-      <c r="E157" s="2">
-        <v>6</v>
-      </c>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2">
-        <v>287</v>
+      <c r="A157" t="s">
+        <v>362</v>
+      </c>
+      <c r="B157" t="s">
+        <v>361</v>
+      </c>
+      <c r="D157" t="s">
+        <v>128</v>
+      </c>
+      <c r="E157">
+        <v>9.9</v>
+      </c>
+      <c r="G157">
+        <v>160</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="B158" t="s">
-        <v>359</v>
+        <v>363</v>
+      </c>
+      <c r="D158" t="s">
+        <v>347</v>
       </c>
       <c r="E158">
-        <v>2</v>
+        <v>9.9</v>
       </c>
       <c r="G158">
-        <v>137</v>
+        <v>161</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="B159" t="s">
-        <v>361</v>
+        <v>365</v>
+      </c>
+      <c r="D159" t="s">
+        <v>256</v>
       </c>
       <c r="E159">
-        <v>2</v>
+        <v>22.9</v>
       </c>
       <c r="G159">
-        <v>138</v>
+        <v>162</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>859</v>
+        <v>368</v>
       </c>
       <c r="B160" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E160">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="G160">
-        <v>139</v>
+        <v>163</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>860</v>
+        <v>370</v>
       </c>
       <c r="B161" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="E161">
-        <v>88</v>
+        <v>18.5</v>
       </c>
       <c r="G161">
-        <v>140</v>
+        <v>164</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="B162" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="E162">
-        <v>1</v>
+        <v>26.5</v>
       </c>
       <c r="G162">
-        <v>141</v>
+        <v>165</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="B163" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="E163">
-        <v>1.9</v>
+        <v>45</v>
       </c>
       <c r="G163">
-        <v>142</v>
+        <v>166</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="B164" t="s">
-        <v>368</v>
-      </c>
-      <c r="C164" t="s">
-        <v>369</v>
-      </c>
-      <c r="D164" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E164">
-        <v>26.9</v>
+        <v>47</v>
       </c>
       <c r="G164">
-        <v>143</v>
+        <v>167</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="B165" t="s">
-        <v>371</v>
-      </c>
-      <c r="C165" t="s">
-        <v>372</v>
-      </c>
-      <c r="D165" t="s">
-        <v>304</v>
+        <v>377</v>
       </c>
       <c r="E165">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G165">
-        <v>144</v>
+        <v>168</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B166" t="s">
-        <v>374</v>
-      </c>
-      <c r="C166" t="s">
-        <v>375</v>
-      </c>
-      <c r="D166" t="s">
-        <v>304</v>
+        <v>379</v>
       </c>
       <c r="E166">
-        <v>36.5</v>
+        <v>77</v>
       </c>
       <c r="G166">
-        <v>145</v>
+        <v>169</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="B167" t="s">
-        <v>377</v>
-      </c>
-      <c r="D167" t="s">
-        <v>138</v>
+        <v>381</v>
+      </c>
+      <c r="C167" t="s">
+        <v>382</v>
       </c>
       <c r="E167">
-        <v>41.5</v>
+        <v>49.9</v>
       </c>
       <c r="G167">
-        <v>146</v>
+        <v>170</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="B168" t="s">
-        <v>379</v>
-      </c>
-      <c r="D168" t="s">
-        <v>138</v>
+        <v>384</v>
       </c>
       <c r="E168">
-        <v>41.5</v>
+        <v>66</v>
       </c>
       <c r="G168">
-        <v>147</v>
+        <v>171</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B169" t="s">
-        <v>381</v>
-      </c>
-      <c r="D169" t="s">
-        <v>304</v>
+        <v>386</v>
       </c>
       <c r="E169">
-        <v>37.5</v>
+        <v>66</v>
       </c>
       <c r="G169">
-        <v>148</v>
+        <v>172</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="B170" t="s">
-        <v>383</v>
-      </c>
-      <c r="D170" t="s">
-        <v>304</v>
+        <v>388</v>
+      </c>
+      <c r="C170" t="s">
+        <v>389</v>
       </c>
       <c r="E170">
-        <v>37.5</v>
+        <v>59.9</v>
       </c>
       <c r="G170">
-        <v>149</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B171" t="s">
-        <v>385</v>
+        <v>391</v>
+      </c>
+      <c r="C171" t="s">
+        <v>392</v>
       </c>
       <c r="D171" t="s">
-        <v>304</v>
+        <v>393</v>
       </c>
       <c r="E171">
-        <v>36</v>
+        <v>62.5</v>
       </c>
       <c r="G171">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="B172" t="s">
-        <v>387</v>
+        <v>395</v>
+      </c>
+      <c r="C172" t="s">
+        <v>392</v>
       </c>
       <c r="D172" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="E172">
-        <v>36</v>
+        <v>62.5</v>
       </c>
       <c r="G172">
-        <v>151</v>
+        <v>175</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B173" t="s">
-        <v>390</v>
-      </c>
-      <c r="D173" t="s">
-        <v>388</v>
+        <v>397</v>
+      </c>
+      <c r="C173" t="s">
+        <v>392</v>
       </c>
       <c r="E173">
-        <v>42</v>
+        <v>64.5</v>
       </c>
       <c r="G173">
-        <v>152</v>
+        <v>176</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="B174" t="s">
+        <v>399</v>
+      </c>
+      <c r="C174" t="s">
         <v>392</v>
       </c>
-      <c r="D174" t="s">
-        <v>304</v>
-      </c>
       <c r="E174">
-        <v>42</v>
+        <v>68.8</v>
       </c>
       <c r="G174">
-        <v>153</v>
+        <v>177</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="B175" t="s">
-        <v>394</v>
-      </c>
-      <c r="D175" t="s">
-        <v>395</v>
+        <v>401</v>
+      </c>
+      <c r="C175" t="s">
+        <v>392</v>
       </c>
       <c r="E175">
-        <v>86</v>
+        <v>68.8</v>
       </c>
       <c r="G175">
-        <v>154</v>
+        <v>178</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B176" t="s">
-        <v>397</v>
-      </c>
-      <c r="D176" t="s">
-        <v>304</v>
+        <v>403</v>
+      </c>
+      <c r="C176" t="s">
+        <v>392</v>
       </c>
       <c r="E176">
-        <v>86</v>
+        <v>68.8</v>
       </c>
       <c r="G176">
-        <v>155</v>
+        <v>179</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="B177" t="s">
-        <v>399</v>
-      </c>
-      <c r="D177" t="s">
-        <v>388</v>
+        <v>405</v>
       </c>
       <c r="E177">
-        <v>324</v>
+        <v>12</v>
       </c>
       <c r="G177">
-        <v>156</v>
+        <v>180</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
       <c r="B178" t="s">
-        <v>401</v>
-      </c>
-      <c r="D178" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
       <c r="E178">
-        <v>37.5</v>
+        <v>16</v>
       </c>
       <c r="G178">
-        <v>157</v>
+        <v>181</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="B179" t="s">
-        <v>404</v>
-      </c>
-      <c r="D179" t="s">
-        <v>405</v>
+        <v>409</v>
+      </c>
+      <c r="C179" t="s">
+        <v>410</v>
       </c>
       <c r="E179">
-        <v>42</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G179">
-        <v>158</v>
+        <v>182</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
       <c r="B180" t="s">
-        <v>407</v>
-      </c>
-      <c r="D180" t="s">
-        <v>138</v>
+        <v>412</v>
       </c>
       <c r="E180">
-        <v>8.8000000000000007</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G180">
-        <v>159</v>
+        <v>183</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="B181" t="s">
-        <v>409</v>
-      </c>
-      <c r="D181" t="s">
-        <v>129</v>
+        <v>414</v>
+      </c>
+      <c r="C181" t="s">
+        <v>415</v>
       </c>
       <c r="E181">
-        <v>9.9</v>
+        <v>22</v>
       </c>
       <c r="G181">
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="B182" t="s">
-        <v>411</v>
-      </c>
-      <c r="D182" t="s">
-        <v>395</v>
+        <v>417</v>
       </c>
       <c r="E182">
-        <v>9.9</v>
+        <v>72</v>
       </c>
       <c r="G182">
-        <v>161</v>
+        <v>185</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="B183" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="D183" t="s">
-        <v>304</v>
+        <v>420</v>
       </c>
       <c r="E183">
-        <v>22.9</v>
+        <v>10.5</v>
       </c>
       <c r="G183">
-        <v>162</v>
+        <v>186</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>416</v>
+        <v>423</v>
       </c>
       <c r="B184" t="s">
-        <v>415</v>
+        <v>422</v>
       </c>
       <c r="E184">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="G184">
-        <v>163</v>
+        <v>187</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>418</v>
+        <v>425</v>
       </c>
       <c r="B185" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="E185">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="G185">
-        <v>164</v>
+        <v>188</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>420</v>
+        <v>427</v>
       </c>
       <c r="B186" t="s">
-        <v>419</v>
+        <v>426</v>
+      </c>
+      <c r="D186" t="s">
+        <v>256</v>
       </c>
       <c r="E186">
-        <v>26.5</v>
+        <v>17.5</v>
       </c>
       <c r="G186">
-        <v>165</v>
+        <v>189</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="B187" t="s">
-        <v>421</v>
+        <v>428</v>
+      </c>
+      <c r="D187" t="s">
+        <v>256</v>
       </c>
       <c r="E187">
-        <v>45</v>
+        <v>16.8</v>
       </c>
       <c r="G187">
-        <v>166</v>
+        <v>190</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="B188" t="s">
-        <v>423</v>
+        <v>430</v>
+      </c>
+      <c r="C188" t="s">
+        <v>431</v>
+      </c>
+      <c r="D188" t="s">
+        <v>256</v>
       </c>
       <c r="E188">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="G188">
-        <v>167</v>
+        <v>191</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="B189" t="s">
-        <v>425</v>
+        <v>433</v>
+      </c>
+      <c r="D189" t="s">
+        <v>434</v>
       </c>
       <c r="E189">
-        <v>13</v>
+        <v>7.5</v>
       </c>
       <c r="G189">
-        <v>168</v>
+        <v>192</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
-        <v>428</v>
+        <v>438</v>
       </c>
       <c r="B190" t="s">
-        <v>427</v>
+        <v>436</v>
+      </c>
+      <c r="D190" t="s">
+        <v>437</v>
       </c>
       <c r="E190">
-        <v>77</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G190">
-        <v>169</v>
+        <v>193</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="B191" t="s">
-        <v>429</v>
-      </c>
-      <c r="C191" t="s">
-        <v>430</v>
+        <v>439</v>
+      </c>
+      <c r="D191" t="s">
+        <v>357</v>
       </c>
       <c r="E191">
-        <v>49.9</v>
+        <v>6.5</v>
       </c>
       <c r="G191">
-        <v>170</v>
+        <v>194</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="B192" t="s">
-        <v>432</v>
+        <v>441</v>
+      </c>
+      <c r="D192" t="s">
+        <v>357</v>
       </c>
       <c r="E192">
-        <v>66</v>
+        <v>7.5</v>
       </c>
       <c r="G192">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="193" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B193" t="s">
-        <v>434</v>
+        <v>443</v>
+      </c>
+      <c r="D193" t="s">
+        <v>437</v>
       </c>
       <c r="E193">
-        <v>66</v>
+        <v>7.9</v>
       </c>
       <c r="G193">
-        <v>172</v>
+        <v>196</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B194" t="s">
-        <v>436</v>
-      </c>
-      <c r="C194" t="s">
+        <v>445</v>
+      </c>
+      <c r="D194" t="s">
         <v>437</v>
       </c>
       <c r="E194">
-        <v>59.9</v>
+        <v>10.199999999999999</v>
       </c>
       <c r="G194">
-        <v>173</v>
+        <v>196</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
-        <v>442</v>
+        <v>449</v>
       </c>
       <c r="B195" t="s">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="C195" t="s">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="D195" t="s">
-        <v>441</v>
+        <v>393</v>
       </c>
       <c r="E195">
-        <v>62.5</v>
+        <v>59</v>
       </c>
       <c r="G195">
-        <v>174</v>
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B196" t="s">
-        <v>443</v>
+        <v>450</v>
       </c>
       <c r="C196" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="D196" t="s">
-        <v>441</v>
+        <v>393</v>
       </c>
       <c r="E196">
-        <v>62.5</v>
+        <v>59.9</v>
       </c>
       <c r="G196">
-        <v>175</v>
+        <v>196</v>
       </c>
     </row>
     <row r="197" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B197" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="C197" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="E197">
-        <v>64.5</v>
+        <v>12.5</v>
       </c>
       <c r="G197">
-        <v>176</v>
+        <v>197</v>
       </c>
     </row>
     <row r="198" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="B198" t="s">
-        <v>447</v>
-      </c>
-      <c r="C198" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="E198">
-        <v>68.8</v>
+        <v>129.9</v>
       </c>
       <c r="G198">
-        <v>177</v>
+        <v>198</v>
       </c>
     </row>
     <row r="199" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B199" t="s">
-        <v>449</v>
-      </c>
-      <c r="C199" t="s">
-        <v>440</v>
+        <v>457</v>
       </c>
       <c r="E199">
-        <v>68.8</v>
+        <v>17</v>
       </c>
       <c r="G199">
-        <v>178</v>
+        <v>199</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
-        <v>452</v>
+        <v>460</v>
       </c>
       <c r="B200" t="s">
-        <v>451</v>
-      </c>
-      <c r="C200" t="s">
-        <v>440</v>
+        <v>459</v>
+      </c>
+      <c r="D200" t="s">
+        <v>256</v>
       </c>
       <c r="E200">
-        <v>68.8</v>
+        <v>49.9</v>
       </c>
       <c r="G200">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="201" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="B201" t="s">
-        <v>453</v>
+        <v>461</v>
+      </c>
+      <c r="D201" t="s">
+        <v>420</v>
       </c>
       <c r="E201">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="G201">
-        <v>180</v>
+        <v>201</v>
       </c>
     </row>
     <row r="202" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B202" t="s">
-        <v>455</v>
+        <v>463</v>
+      </c>
+      <c r="D202" t="s">
+        <v>256</v>
       </c>
       <c r="E202">
-        <v>16</v>
+        <v>72</v>
       </c>
       <c r="G202">
-        <v>181</v>
+        <v>202</v>
       </c>
     </row>
     <row r="203" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="B203" t="s">
-        <v>457</v>
-      </c>
-      <c r="C203" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="E203">
-        <v>19.899999999999999</v>
+        <v>18</v>
       </c>
       <c r="G203">
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="204" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
-        <v>461</v>
+        <v>795</v>
       </c>
       <c r="B204" t="s">
-        <v>460</v>
+        <v>467</v>
       </c>
       <c r="E204">
-        <v>19.899999999999999</v>
+        <v>14</v>
       </c>
       <c r="G204">
-        <v>183</v>
+        <v>204</v>
       </c>
     </row>
     <row r="205" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B205" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="C205" t="s">
-        <v>463</v>
+        <v>470</v>
       </c>
       <c r="E205">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="G205">
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="206" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B206" t="s">
-        <v>465</v>
+        <v>472</v>
       </c>
       <c r="E206">
-        <v>72</v>
+        <v>8.5</v>
       </c>
       <c r="G206">
-        <v>185</v>
+        <v>206</v>
       </c>
     </row>
     <row r="207" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="B207" t="s">
-        <v>467</v>
-      </c>
-      <c r="D207" t="s">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="E207">
-        <v>10.5</v>
+        <v>8.5</v>
       </c>
       <c r="G207">
-        <v>186</v>
+        <v>207</v>
       </c>
     </row>
     <row r="208" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B208" t="s">
-        <v>470</v>
+        <v>476</v>
+      </c>
+      <c r="C208" t="s">
+        <v>477</v>
       </c>
       <c r="E208">
-        <v>19</v>
+        <v>29.9</v>
       </c>
       <c r="G208">
-        <v>187</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="B209" t="s">
-        <v>472</v>
+        <v>479</v>
+      </c>
+      <c r="C209" t="s">
+        <v>477</v>
       </c>
       <c r="E209">
-        <v>14</v>
+        <v>29.9</v>
       </c>
       <c r="G209">
-        <v>188</v>
+        <v>209</v>
       </c>
     </row>
     <row r="210" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="B210" t="s">
-        <v>474</v>
-      </c>
-      <c r="D210" t="s">
-        <v>304</v>
+        <v>481</v>
+      </c>
+      <c r="C210" t="s">
+        <v>482</v>
       </c>
       <c r="E210">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="G210">
-        <v>189</v>
+        <v>210</v>
       </c>
     </row>
     <row r="211" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B211" t="s">
-        <v>476</v>
-      </c>
-      <c r="D211" t="s">
-        <v>304</v>
+        <v>484</v>
+      </c>
+      <c r="C211" t="s">
+        <v>482</v>
       </c>
       <c r="E211">
-        <v>16.8</v>
+        <v>18</v>
       </c>
       <c r="G211">
-        <v>190</v>
+        <v>211</v>
       </c>
     </row>
     <row r="212" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
       <c r="B212" t="s">
-        <v>478</v>
-      </c>
-      <c r="C212" t="s">
-        <v>479</v>
-      </c>
-      <c r="D212" t="s">
-        <v>304</v>
+        <v>486</v>
       </c>
       <c r="E212">
-        <v>58</v>
+        <v>13</v>
       </c>
       <c r="G212">
-        <v>191</v>
+        <v>212</v>
       </c>
     </row>
     <row r="213" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B213" t="s">
-        <v>481</v>
-      </c>
-      <c r="D213" t="s">
-        <v>482</v>
+        <v>488</v>
+      </c>
+      <c r="C213" t="s">
+        <v>489</v>
       </c>
       <c r="E213">
-        <v>7.5</v>
+        <v>17</v>
       </c>
       <c r="G213">
-        <v>192</v>
+        <v>213</v>
       </c>
     </row>
     <row r="214" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B214" t="s">
-        <v>484</v>
-      </c>
-      <c r="D214" t="s">
-        <v>485</v>
+        <v>491</v>
+      </c>
+      <c r="C214" t="s">
+        <v>489</v>
       </c>
       <c r="E214">
-        <v>19.899999999999999</v>
+        <v>17</v>
       </c>
       <c r="G214">
-        <v>193</v>
+        <v>214</v>
       </c>
     </row>
     <row r="215" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B215" t="s">
-        <v>487</v>
-      </c>
-      <c r="D215" t="s">
-        <v>405</v>
+        <v>493</v>
       </c>
       <c r="E215">
-        <v>6.5</v>
+        <v>17</v>
       </c>
       <c r="G215">
-        <v>194</v>
+        <v>215</v>
       </c>
     </row>
     <row r="216" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B216" t="s">
-        <v>489</v>
-      </c>
-      <c r="D216" t="s">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="E216">
-        <v>7.5</v>
+        <v>17</v>
       </c>
       <c r="G216">
-        <v>195</v>
+        <v>216</v>
       </c>
     </row>
     <row r="217" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B217" t="s">
-        <v>491</v>
-      </c>
-      <c r="D217" t="s">
-        <v>485</v>
+        <v>497</v>
+      </c>
+      <c r="C217" t="s">
+        <v>498</v>
       </c>
       <c r="E217">
-        <v>7.9</v>
+        <v>38</v>
       </c>
       <c r="G217">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="218" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B218" t="s">
-        <v>493</v>
-      </c>
-      <c r="D218" t="s">
-        <v>485</v>
+        <v>500</v>
+      </c>
+      <c r="C218" t="s">
+        <v>498</v>
       </c>
       <c r="E218">
-        <v>10.199999999999999</v>
+        <v>38</v>
       </c>
       <c r="G218">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B219" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="C219" t="s">
-        <v>496</v>
-      </c>
-      <c r="D219" t="s">
-        <v>441</v>
+        <v>498</v>
       </c>
       <c r="E219">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G219">
-        <v>196</v>
+        <v>210</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B220" t="s">
+        <v>504</v>
+      </c>
+      <c r="C220" t="s">
         <v>498</v>
       </c>
-      <c r="C220" t="s">
-        <v>499</v>
-      </c>
-      <c r="D220" t="s">
-        <v>441</v>
-      </c>
       <c r="E220">
-        <v>59.9</v>
+        <v>37</v>
       </c>
       <c r="G220">
-        <v>196</v>
+        <v>211</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="B221" t="s">
-        <v>501</v>
-      </c>
-      <c r="C221" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="E221">
-        <v>12.5</v>
+        <v>14</v>
       </c>
       <c r="G221">
-        <v>197</v>
+        <v>217</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B222" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E222">
-        <v>129.9</v>
+        <v>14</v>
       </c>
       <c r="G222">
-        <v>198</v>
+        <v>218</v>
       </c>
     </row>
     <row r="223" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B223" t="s">
-        <v>505</v>
+        <v>510</v>
+      </c>
+      <c r="C223" t="s">
+        <v>511</v>
       </c>
       <c r="E223">
-        <v>17</v>
+        <v>9.9</v>
       </c>
       <c r="G223">
-        <v>199</v>
+        <v>219</v>
       </c>
     </row>
     <row r="224" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B224" t="s">
-        <v>507</v>
-      </c>
-      <c r="D224" t="s">
-        <v>304</v>
+        <v>513</v>
+      </c>
+      <c r="C224" t="s">
+        <v>511</v>
       </c>
       <c r="E224">
-        <v>49.9</v>
+        <v>9.9</v>
       </c>
       <c r="G224">
-        <v>200</v>
+        <v>220</v>
       </c>
     </row>
     <row r="225" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B225" t="s">
-        <v>509</v>
-      </c>
-      <c r="D225" t="s">
-        <v>468</v>
+        <v>515</v>
+      </c>
+      <c r="C225" t="s">
+        <v>498</v>
       </c>
       <c r="E225">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="G225">
-        <v>201</v>
+        <v>221</v>
       </c>
     </row>
     <row r="226" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B226" t="s">
-        <v>511</v>
-      </c>
-      <c r="D226" t="s">
-        <v>304</v>
+        <v>517</v>
+      </c>
+      <c r="C226" t="s">
+        <v>498</v>
       </c>
       <c r="E226">
-        <v>72</v>
+        <v>27</v>
       </c>
       <c r="G226">
-        <v>202</v>
+        <v>222</v>
       </c>
     </row>
     <row r="227" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B227" t="s">
-        <v>513</v>
+        <v>519</v>
+      </c>
+      <c r="C227" t="s">
+        <v>498</v>
       </c>
       <c r="E227">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="G227">
-        <v>203</v>
+        <v>223</v>
       </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
-        <v>861</v>
+        <v>520</v>
       </c>
       <c r="B228" t="s">
-        <v>515</v>
+        <v>521</v>
+      </c>
+      <c r="C228" t="s">
+        <v>498</v>
       </c>
       <c r="E228">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="G228">
-        <v>204</v>
+        <v>224</v>
       </c>
     </row>
     <row r="229" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
-        <v>516</v>
+        <v>522</v>
       </c>
       <c r="B229" t="s">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="C229" t="s">
-        <v>518</v>
+        <v>498</v>
       </c>
       <c r="E229">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G229">
-        <v>205</v>
+        <v>225</v>
       </c>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
-        <v>519</v>
+        <v>524</v>
       </c>
       <c r="B230" t="s">
-        <v>520</v>
+        <v>525</v>
+      </c>
+      <c r="C230" t="s">
+        <v>498</v>
       </c>
       <c r="E230">
-        <v>8.5</v>
+        <v>45</v>
       </c>
       <c r="G230">
-        <v>206</v>
+        <v>226</v>
       </c>
     </row>
     <row r="231" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
-        <v>521</v>
+        <v>526</v>
       </c>
       <c r="B231" t="s">
-        <v>522</v>
+        <v>527</v>
+      </c>
+      <c r="C231" t="s">
+        <v>498</v>
       </c>
       <c r="E231">
-        <v>8.5</v>
+        <v>38</v>
       </c>
       <c r="G231">
-        <v>207</v>
+        <v>227</v>
       </c>
     </row>
     <row r="232" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B232" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="C232" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="E232">
-        <v>29.9</v>
+        <v>38</v>
       </c>
       <c r="G232">
-        <v>208</v>
+        <v>228</v>
       </c>
     </row>
     <row r="233" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B233" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C233" t="s">
-        <v>525</v>
+        <v>498</v>
       </c>
       <c r="E233">
-        <v>29.9</v>
+        <v>37</v>
       </c>
       <c r="G233">
-        <v>209</v>
+        <v>229</v>
       </c>
     </row>
     <row r="234" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B234" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C234" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="E234">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="G234">
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="235" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="B235" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="C235" t="s">
-        <v>530</v>
+        <v>498</v>
       </c>
       <c r="E235">
-        <v>18</v>
+        <v>49.9</v>
       </c>
       <c r="G235">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="236" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="B236" t="s">
-        <v>534</v>
+        <v>537</v>
+      </c>
+      <c r="C236" t="s">
+        <v>498</v>
       </c>
       <c r="E236">
-        <v>13</v>
+        <v>49.9</v>
       </c>
       <c r="G236">
-        <v>212</v>
+        <v>232</v>
       </c>
     </row>
     <row r="237" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B237" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="C237" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="E237">
-        <v>17</v>
+        <v>9.9</v>
       </c>
       <c r="G237">
-        <v>213</v>
+        <v>233</v>
       </c>
     </row>
     <row r="238" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B238" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C238" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="E238">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="G238">
-        <v>214</v>
+        <v>234</v>
       </c>
     </row>
     <row r="239" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B239" t="s">
-        <v>541</v>
+        <v>545</v>
+      </c>
+      <c r="C239" t="s">
+        <v>543</v>
       </c>
       <c r="E239">
-        <v>17</v>
+        <v>13.5</v>
       </c>
       <c r="G239">
-        <v>215</v>
+        <v>235</v>
       </c>
     </row>
     <row r="240" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B240" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="E240">
-        <v>17</v>
+        <v>14.5</v>
       </c>
       <c r="G240">
-        <v>216</v>
+        <v>236</v>
       </c>
     </row>
     <row r="241" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B241" t="s">
-        <v>545</v>
-      </c>
-      <c r="C241" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="E241">
-        <v>38</v>
+        <v>14.5</v>
       </c>
       <c r="G241">
-        <v>210</v>
+        <v>237</v>
       </c>
     </row>
     <row r="242" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
-        <v>547</v>
+        <v>848</v>
       </c>
       <c r="B242" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="C242" t="s">
-        <v>546</v>
+        <v>552</v>
       </c>
       <c r="E242">
-        <v>38</v>
+        <v>9.9</v>
       </c>
       <c r="G242">
-        <v>211</v>
+        <v>238</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
-        <v>549</v>
+        <v>849</v>
       </c>
       <c r="B243" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="C243" t="s">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="E243">
-        <v>37</v>
+        <v>7.5</v>
       </c>
       <c r="G243">
-        <v>210</v>
+        <v>239</v>
       </c>
     </row>
     <row r="244" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
-        <v>551</v>
+        <v>850</v>
       </c>
       <c r="B244" t="s">
-        <v>552</v>
-      </c>
-      <c r="C244" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="E244">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="G244">
-        <v>211</v>
+        <v>240</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
-        <v>553</v>
+        <v>851</v>
       </c>
       <c r="B245" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="E245">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="G245">
-        <v>217</v>
+        <v>241</v>
       </c>
     </row>
     <row r="246" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
-        <v>555</v>
+        <v>317</v>
       </c>
       <c r="B246" t="s">
-        <v>556</v>
+        <v>559</v>
+      </c>
+      <c r="C246" t="s">
+        <v>560</v>
       </c>
       <c r="E246">
-        <v>14</v>
+        <v>110</v>
       </c>
       <c r="G246">
-        <v>218</v>
+        <v>242</v>
       </c>
     </row>
     <row r="247" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
-        <v>557</v>
+        <v>550</v>
       </c>
       <c r="B247" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="C247" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E247">
-        <v>9.9</v>
+        <v>113</v>
       </c>
       <c r="G247">
-        <v>219</v>
+        <v>243</v>
       </c>
     </row>
     <row r="248" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
+        <v>553</v>
+      </c>
+      <c r="B248" t="s">
+        <v>562</v>
+      </c>
+      <c r="C248" t="s">
         <v>560</v>
       </c>
-      <c r="B248" t="s">
-        <v>561</v>
-      </c>
-      <c r="C248" t="s">
-        <v>559</v>
-      </c>
       <c r="E248">
-        <v>9.9</v>
+        <v>113</v>
       </c>
       <c r="G248">
-        <v>220</v>
+        <v>244</v>
       </c>
     </row>
     <row r="249" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
-        <v>562</v>
+        <v>796</v>
       </c>
       <c r="B249" t="s">
         <v>563</v>
       </c>
       <c r="C249" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="E249">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="G249">
-        <v>221</v>
+        <v>245</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
-        <v>564</v>
+        <v>797</v>
       </c>
       <c r="B250" t="s">
         <v>565</v>
       </c>
       <c r="C250" t="s">
-        <v>546</v>
+        <v>564</v>
       </c>
       <c r="E250">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="G250">
-        <v>222</v>
+        <v>246</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
+        <v>798</v>
+      </c>
+      <c r="B251" t="s">
         <v>566</v>
       </c>
-      <c r="B251" t="s">
-        <v>567</v>
-      </c>
-      <c r="C251" t="s">
-        <v>546</v>
-      </c>
       <c r="E251">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G251">
-        <v>223</v>
+        <v>247</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
-        <v>568</v>
+        <v>799</v>
       </c>
       <c r="B252" t="s">
-        <v>569</v>
-      </c>
-      <c r="C252" t="s">
-        <v>546</v>
+        <v>567</v>
       </c>
       <c r="E252">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="G252">
-        <v>224</v>
+        <v>248</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
-        <v>570</v>
+        <v>851</v>
       </c>
       <c r="B253" t="s">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="C253" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E253">
-        <v>45</v>
+        <v>349.9</v>
       </c>
       <c r="G253">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
-        <v>572</v>
+        <v>852</v>
       </c>
       <c r="B254" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="C254" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E254">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="G254">
-        <v>226</v>
+        <v>252</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
-        <v>574</v>
+        <v>853</v>
       </c>
       <c r="B255" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C255" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E255">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G255">
-        <v>227</v>
+        <v>253</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
-        <v>576</v>
+        <v>854</v>
       </c>
       <c r="B256" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="C256" t="s">
-        <v>546</v>
+        <v>573</v>
       </c>
       <c r="E256">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="G256">
-        <v>228</v>
+        <v>254</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
-        <v>578</v>
+        <v>855</v>
       </c>
       <c r="B257" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="C257" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E257">
-        <v>37</v>
+        <v>65</v>
       </c>
       <c r="G257">
-        <v>229</v>
+        <v>255</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
-        <v>580</v>
+        <v>856</v>
       </c>
       <c r="B258" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="C258" t="s">
-        <v>546</v>
+        <v>569</v>
       </c>
       <c r="E258">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="G258">
-        <v>230</v>
+        <v>256</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
-        <v>582</v>
+        <v>857</v>
       </c>
       <c r="B259" t="s">
-        <v>583</v>
+        <v>576</v>
       </c>
       <c r="C259" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="E259">
-        <v>49.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G259">
-        <v>231</v>
+        <v>257</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
-        <v>584</v>
+        <v>858</v>
       </c>
       <c r="B260" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="C260" t="s">
-        <v>546</v>
+        <v>577</v>
       </c>
       <c r="E260">
-        <v>49.9</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G260">
-        <v>232</v>
+        <v>258</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
-        <v>586</v>
+        <v>859</v>
       </c>
       <c r="B261" t="s">
-        <v>587</v>
-      </c>
-      <c r="C261" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
       <c r="E261">
-        <v>9.9</v>
+        <v>35</v>
       </c>
       <c r="G261">
-        <v>233</v>
+        <v>259</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
-        <v>589</v>
+        <v>860</v>
       </c>
       <c r="B262" t="s">
-        <v>590</v>
-      </c>
-      <c r="C262" t="s">
-        <v>591</v>
+        <v>580</v>
       </c>
       <c r="E262">
-        <v>13.5</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G262">
-        <v>234</v>
+        <v>259</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
-        <v>592</v>
+        <v>800</v>
       </c>
       <c r="B263" t="s">
-        <v>593</v>
-      </c>
-      <c r="C263" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="E263">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="G263">
-        <v>235</v>
+        <v>260</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
-        <v>594</v>
+        <v>801</v>
       </c>
       <c r="B264" t="s">
-        <v>595</v>
+        <v>584</v>
       </c>
       <c r="E264">
-        <v>14.5</v>
+        <v>5.5</v>
       </c>
       <c r="G264">
-        <v>236</v>
+        <v>261</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
-        <v>596</v>
+        <v>802</v>
       </c>
       <c r="B265" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="E265">
-        <v>14.5</v>
+        <v>7</v>
       </c>
       <c r="G265">
-        <v>237</v>
+        <v>262</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
-        <v>916</v>
+        <v>556</v>
       </c>
       <c r="B266" t="s">
-        <v>599</v>
-      </c>
-      <c r="C266" t="s">
-        <v>600</v>
+        <v>588</v>
       </c>
       <c r="E266">
-        <v>9.9</v>
+        <v>2.5</v>
       </c>
       <c r="G266">
-        <v>238</v>
+        <v>263</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
-        <v>917</v>
+        <v>861</v>
       </c>
       <c r="B267" t="s">
-        <v>602</v>
+        <v>590</v>
       </c>
       <c r="C267" t="s">
-        <v>603</v>
+        <v>591</v>
       </c>
       <c r="E267">
         <v>7.5</v>
       </c>
       <c r="G267">
-        <v>239</v>
+        <v>264</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
-        <v>918</v>
+        <v>862</v>
       </c>
       <c r="B268" t="s">
-        <v>605</v>
+        <v>593</v>
+      </c>
+      <c r="C268" t="s">
+        <v>594</v>
       </c>
       <c r="E268">
-        <v>78</v>
+        <v>8.5</v>
       </c>
       <c r="G268">
-        <v>240</v>
+        <v>265</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
-        <v>919</v>
+        <v>863</v>
       </c>
       <c r="B269" t="s">
-        <v>606</v>
+        <v>595</v>
       </c>
       <c r="E269">
-        <v>55</v>
+        <v>17</v>
       </c>
       <c r="G269">
-        <v>241</v>
+        <v>266</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
-        <v>365</v>
+        <v>864</v>
       </c>
       <c r="B270" t="s">
-        <v>607</v>
-      </c>
-      <c r="C270" t="s">
-        <v>608</v>
+        <v>596</v>
       </c>
       <c r="E270">
-        <v>110</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G270">
-        <v>242</v>
+        <v>267</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
-        <v>598</v>
+        <v>865</v>
       </c>
       <c r="B271" t="s">
-        <v>609</v>
-      </c>
-      <c r="C271" t="s">
-        <v>608</v>
+        <v>597</v>
       </c>
       <c r="E271">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="G271">
-        <v>243</v>
+        <v>268</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
-        <v>601</v>
+        <v>866</v>
       </c>
       <c r="B272" t="s">
-        <v>610</v>
-      </c>
-      <c r="C272" t="s">
-        <v>608</v>
+        <v>598</v>
       </c>
       <c r="E272">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="G272">
-        <v>244</v>
+        <v>269</v>
       </c>
     </row>
     <row r="273" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
-        <v>862</v>
+        <v>867</v>
       </c>
       <c r="B273" t="s">
-        <v>611</v>
-      </c>
-      <c r="C273" t="s">
-        <v>612</v>
+        <v>599</v>
       </c>
       <c r="E273">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="G273">
-        <v>245</v>
+        <v>270</v>
       </c>
     </row>
     <row r="274" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
-        <v>863</v>
+        <v>868</v>
       </c>
       <c r="B274" t="s">
-        <v>613</v>
-      </c>
-      <c r="C274" t="s">
-        <v>612</v>
+        <v>600</v>
       </c>
       <c r="E274">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G274">
-        <v>246</v>
+        <v>271</v>
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
-        <v>864</v>
+        <v>869</v>
       </c>
       <c r="B275" t="s">
-        <v>614</v>
+        <v>601</v>
       </c>
       <c r="E275">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="G275">
-        <v>247</v>
+        <v>272</v>
       </c>
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
-        <v>865</v>
+        <v>870</v>
       </c>
       <c r="B276" t="s">
-        <v>615</v>
+        <v>602</v>
       </c>
       <c r="E276">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="G276">
-        <v>248</v>
+        <v>273</v>
       </c>
     </row>
     <row r="277" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
-        <v>866</v>
+        <v>871</v>
       </c>
       <c r="B277" t="s">
-        <v>616</v>
+        <v>603</v>
       </c>
       <c r="E277">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="G277">
-        <v>249</v>
+        <v>274</v>
       </c>
     </row>
     <row r="278" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
-        <v>867</v>
+        <v>872</v>
       </c>
       <c r="B278" t="s">
-        <v>617</v>
+        <v>605</v>
       </c>
       <c r="E278">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="G278">
-        <v>250</v>
+        <v>275</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
-        <v>919</v>
+        <v>873</v>
       </c>
       <c r="B279" t="s">
-        <v>618</v>
-      </c>
-      <c r="C279" t="s">
-        <v>619</v>
+        <v>606</v>
       </c>
       <c r="E279">
-        <v>349.9</v>
+        <v>505</v>
       </c>
       <c r="G279">
-        <v>251</v>
+        <v>276</v>
       </c>
     </row>
     <row r="280" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
-        <v>920</v>
+        <v>874</v>
       </c>
       <c r="B280" t="s">
-        <v>620</v>
-      </c>
-      <c r="C280" t="s">
-        <v>619</v>
+        <v>608</v>
       </c>
       <c r="E280">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="G280">
-        <v>252</v>
+        <v>277</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
-        <v>921</v>
+        <v>875</v>
       </c>
       <c r="B281" t="s">
-        <v>621</v>
-      </c>
-      <c r="C281" t="s">
-        <v>619</v>
+        <v>609</v>
       </c>
       <c r="E281">
-        <v>65</v>
+        <v>22</v>
       </c>
       <c r="G281">
-        <v>253</v>
+        <v>278</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
-        <v>922</v>
+        <v>876</v>
       </c>
       <c r="B282" t="s">
-        <v>622</v>
-      </c>
-      <c r="C282" t="s">
-        <v>623</v>
+        <v>611</v>
       </c>
       <c r="E282">
-        <v>65</v>
+        <v>17</v>
       </c>
       <c r="G282">
-        <v>254</v>
+        <v>279</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
-        <v>923</v>
+        <v>877</v>
       </c>
       <c r="B283" t="s">
-        <v>624</v>
-      </c>
-      <c r="C283" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="E283">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="G283">
-        <v>255</v>
+        <v>280</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
-        <v>924</v>
+        <v>878</v>
       </c>
       <c r="B284" t="s">
-        <v>625</v>
-      </c>
-      <c r="C284" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="E284">
-        <v>75</v>
+        <v>39.9</v>
       </c>
       <c r="G284">
-        <v>256</v>
+        <v>281</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
-        <v>925</v>
+        <v>879</v>
       </c>
       <c r="B285" t="s">
-        <v>626</v>
-      </c>
-      <c r="C285" t="s">
-        <v>627</v>
+        <v>615</v>
       </c>
       <c r="E285">
-        <v>19.899999999999999</v>
+        <v>24</v>
       </c>
       <c r="G285">
-        <v>257</v>
+        <v>282</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
-        <v>926</v>
+        <v>880</v>
       </c>
       <c r="B286" t="s">
-        <v>628</v>
-      </c>
-      <c r="C286" t="s">
-        <v>627</v>
+        <v>616</v>
       </c>
       <c r="E286">
-        <v>19.899999999999999</v>
+        <v>19</v>
       </c>
       <c r="G286">
-        <v>258</v>
+        <v>283</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
-        <v>927</v>
+        <v>881</v>
       </c>
       <c r="B287" t="s">
-        <v>629</v>
+        <v>618</v>
       </c>
       <c r="E287">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G287">
-        <v>259</v>
+        <v>284</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
-        <v>928</v>
+        <v>822</v>
       </c>
       <c r="B288" t="s">
-        <v>630</v>
+        <v>625</v>
       </c>
       <c r="E288">
-        <v>19.899999999999999</v>
+        <v>11</v>
       </c>
       <c r="G288">
-        <v>259</v>
+        <v>288</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
-        <v>868</v>
+        <v>823</v>
       </c>
       <c r="B289" t="s">
-        <v>632</v>
+        <v>627</v>
       </c>
       <c r="E289">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G289">
-        <v>260</v>
+        <v>289</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
-        <v>869</v>
+        <v>824</v>
       </c>
       <c r="B290" t="s">
-        <v>634</v>
+        <v>629</v>
+      </c>
+      <c r="C290" t="s">
+        <v>630</v>
       </c>
       <c r="E290">
-        <v>5.5</v>
+        <v>88</v>
       </c>
       <c r="G290">
-        <v>261</v>
+        <v>290</v>
       </c>
     </row>
     <row r="291" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
-        <v>870</v>
+        <v>825</v>
       </c>
       <c r="B291" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="E291">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G291">
-        <v>262</v>
+        <v>291</v>
       </c>
     </row>
     <row r="292" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
-        <v>604</v>
+        <v>826</v>
       </c>
       <c r="B292" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E292">
-        <v>2.5</v>
+        <v>16</v>
       </c>
       <c r="G292">
-        <v>263</v>
+        <v>292</v>
       </c>
     </row>
     <row r="293" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
-        <v>929</v>
+        <v>827</v>
       </c>
       <c r="B293" t="s">
-        <v>640</v>
-      </c>
-      <c r="C293" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="E293">
-        <v>7.5</v>
+        <v>18</v>
       </c>
       <c r="G293">
-        <v>264</v>
+        <v>293</v>
       </c>
     </row>
     <row r="294" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
-        <v>930</v>
+        <v>828</v>
       </c>
       <c r="B294" t="s">
-        <v>643</v>
+        <v>638</v>
       </c>
       <c r="C294" t="s">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="E294">
-        <v>8.5</v>
+        <v>28</v>
       </c>
       <c r="G294">
-        <v>265</v>
+        <v>294</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
-        <v>931</v>
+        <v>829</v>
       </c>
       <c r="B295" t="s">
-        <v>645</v>
+        <v>641</v>
+      </c>
+      <c r="C295" t="s">
+        <v>642</v>
       </c>
       <c r="E295">
-        <v>17</v>
+        <v>88</v>
       </c>
       <c r="G295">
-        <v>266</v>
+        <v>295</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
-        <v>932</v>
+        <v>830</v>
       </c>
       <c r="B296" t="s">
-        <v>646</v>
+        <v>644</v>
+      </c>
+      <c r="C296" t="s">
+        <v>645</v>
       </c>
       <c r="E296">
-        <v>19.899999999999999</v>
+        <v>44</v>
       </c>
       <c r="G296">
-        <v>267</v>
+        <v>296</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
-        <v>933</v>
+        <v>831</v>
       </c>
       <c r="B297" t="s">
         <v>647</v>
       </c>
+      <c r="C297" t="s">
+        <v>648</v>
+      </c>
       <c r="E297">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="G297">
-        <v>268</v>
+        <v>297</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
-        <v>934</v>
+        <v>832</v>
       </c>
       <c r="B298" t="s">
-        <v>648</v>
+        <v>650</v>
+      </c>
+      <c r="C298" t="s">
+        <v>651</v>
       </c>
       <c r="E298">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="G298">
-        <v>269</v>
+        <v>298</v>
       </c>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
-        <v>935</v>
+        <v>833</v>
       </c>
       <c r="B299" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="E299">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="G299">
-        <v>270</v>
+        <v>299</v>
       </c>
     </row>
     <row r="300" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
-        <v>936</v>
+        <v>834</v>
       </c>
       <c r="B300" t="s">
-        <v>650</v>
+        <v>655</v>
+      </c>
+      <c r="C300" t="s">
+        <v>656</v>
       </c>
       <c r="E300">
-        <v>25</v>
+        <v>92</v>
       </c>
       <c r="G300">
-        <v>271</v>
+        <v>300</v>
       </c>
     </row>
     <row r="301" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
-        <v>937</v>
+        <v>581</v>
       </c>
       <c r="B301" t="s">
-        <v>651</v>
+        <v>658</v>
+      </c>
+      <c r="C301" t="s">
+        <v>659</v>
+      </c>
+      <c r="D301" t="s">
+        <v>154</v>
       </c>
       <c r="E301">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G301">
-        <v>272</v>
+        <v>301</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
-        <v>938</v>
+        <v>583</v>
       </c>
       <c r="B302" t="s">
-        <v>652</v>
+        <v>661</v>
+      </c>
+      <c r="C302" t="s">
+        <v>662</v>
+      </c>
+      <c r="D302" t="s">
+        <v>154</v>
       </c>
       <c r="E302">
-        <v>62</v>
+        <v>23</v>
       </c>
       <c r="G302">
-        <v>273</v>
+        <v>302</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
-        <v>939</v>
+        <v>585</v>
       </c>
       <c r="B303" t="s">
-        <v>653</v>
+        <v>664</v>
+      </c>
+      <c r="C303" t="s">
+        <v>665</v>
       </c>
       <c r="E303">
-        <v>126</v>
+        <v>11</v>
       </c>
       <c r="G303">
-        <v>274</v>
+        <v>303</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
-        <v>940</v>
+        <v>587</v>
       </c>
       <c r="B304" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="E304">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="G304">
-        <v>275</v>
+        <v>304</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
-        <v>941</v>
+        <v>589</v>
       </c>
       <c r="B305" t="s">
-        <v>656</v>
+        <v>669</v>
+      </c>
+      <c r="C305" t="s">
+        <v>670</v>
       </c>
       <c r="E305">
-        <v>505</v>
+        <v>11</v>
       </c>
       <c r="G305">
-        <v>276</v>
+        <v>305</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
-        <v>942</v>
+        <v>592</v>
       </c>
       <c r="B306" t="s">
-        <v>658</v>
+        <v>672</v>
+      </c>
+      <c r="C306" t="s">
+        <v>673</v>
       </c>
       <c r="E306">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="G306">
-        <v>277</v>
+        <v>306</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
-        <v>943</v>
+        <v>860</v>
       </c>
       <c r="B307" t="s">
-        <v>659</v>
+        <v>675</v>
       </c>
       <c r="E307">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="G307">
-        <v>278</v>
+        <v>307</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
-        <v>944</v>
+        <v>882</v>
       </c>
       <c r="B308" t="s">
-        <v>661</v>
+        <v>677</v>
       </c>
       <c r="E308">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G308">
-        <v>279</v>
+        <v>308</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
-        <v>945</v>
+        <v>883</v>
       </c>
       <c r="B309" t="s">
-        <v>663</v>
+        <v>679</v>
       </c>
       <c r="E309">
-        <v>27</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G309">
-        <v>280</v>
+        <v>309</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
-        <v>946</v>
+        <v>884</v>
       </c>
       <c r="B310" t="s">
-        <v>664</v>
+        <v>681</v>
       </c>
       <c r="E310">
-        <v>39.9</v>
+        <v>38</v>
       </c>
       <c r="G310">
-        <v>281</v>
+        <v>310</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
-        <v>947</v>
+        <v>885</v>
       </c>
       <c r="B311" t="s">
-        <v>665</v>
+        <v>683</v>
       </c>
       <c r="E311">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="G311">
-        <v>282</v>
+        <v>311</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
-        <v>948</v>
+        <v>886</v>
       </c>
       <c r="B312" t="s">
-        <v>666</v>
+        <v>684</v>
+      </c>
+      <c r="C312" t="s">
+        <v>685</v>
       </c>
       <c r="E312">
-        <v>19</v>
+        <v>26.5</v>
       </c>
       <c r="G312">
-        <v>283</v>
+        <v>312</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
-        <v>949</v>
+        <v>887</v>
       </c>
       <c r="B313" t="s">
-        <v>668</v>
+        <v>687</v>
       </c>
       <c r="E313">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G313">
-        <v>284</v>
+        <v>313</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
-        <v>890</v>
+        <v>847</v>
       </c>
       <c r="B314" t="s">
-        <v>675</v>
+        <v>688</v>
       </c>
       <c r="E314">
-        <v>11</v>
+        <v>157</v>
       </c>
       <c r="G314">
-        <v>288</v>
+        <v>314</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
-        <v>891</v>
+        <v>888</v>
       </c>
       <c r="B315" t="s">
-        <v>677</v>
+        <v>690</v>
       </c>
       <c r="E315">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G315">
-        <v>289</v>
+        <v>315</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="B316" t="s">
-        <v>679</v>
-      </c>
-      <c r="C316" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="E316">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="G316">
-        <v>290</v>
+        <v>316</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="B317" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="E317">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G317">
-        <v>291</v>
+        <v>317</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
-        <v>894</v>
+        <v>604</v>
       </c>
       <c r="B318" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="E318">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="G318">
-        <v>292</v>
+        <v>318</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
-        <v>895</v>
+        <v>803</v>
       </c>
       <c r="B319" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
       <c r="E319">
-        <v>18</v>
+        <v>465</v>
       </c>
       <c r="G319">
-        <v>293</v>
+        <v>319</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
-        <v>896</v>
+        <v>804</v>
       </c>
       <c r="B320" t="s">
-        <v>688</v>
-      </c>
-      <c r="C320" t="s">
-        <v>689</v>
+        <v>699</v>
       </c>
       <c r="E320">
-        <v>28</v>
+        <v>705</v>
       </c>
       <c r="G320">
-        <v>294</v>
+        <v>320</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
-        <v>897</v>
+        <v>607</v>
       </c>
       <c r="B321" t="s">
-        <v>691</v>
-      </c>
-      <c r="C321" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="E321">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="G321">
-        <v>295</v>
+        <v>321</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
-        <v>898</v>
+        <v>805</v>
       </c>
       <c r="B322" t="s">
-        <v>694</v>
-      </c>
-      <c r="C322" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="E322">
-        <v>44</v>
+        <v>145</v>
       </c>
       <c r="G322">
-        <v>296</v>
+        <v>322</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
-        <v>899</v>
+        <v>806</v>
       </c>
       <c r="B323" t="s">
-        <v>697</v>
-      </c>
-      <c r="C323" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="E323">
-        <v>67</v>
+        <v>195</v>
       </c>
       <c r="G323">
-        <v>297</v>
+        <v>323</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
-        <v>900</v>
+        <v>807</v>
       </c>
       <c r="B324" t="s">
-        <v>700</v>
-      </c>
-      <c r="C324" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="E324">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="G324">
-        <v>298</v>
+        <v>324</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
-        <v>901</v>
+        <v>808</v>
       </c>
       <c r="B325" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="E325">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G325">
-        <v>299</v>
+        <v>325</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
-        <v>902</v>
+        <v>610</v>
       </c>
       <c r="B326" t="s">
         <v>705</v>
       </c>
-      <c r="C326" t="s">
-        <v>706</v>
-      </c>
       <c r="E326">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G326">
-        <v>300</v>
+        <v>326</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
-        <v>631</v>
+        <v>809</v>
       </c>
       <c r="B327" t="s">
-        <v>708</v>
-      </c>
-      <c r="C327" t="s">
-        <v>709</v>
-      </c>
-      <c r="D327" t="s">
-        <v>189</v>
+        <v>706</v>
       </c>
       <c r="E327">
-        <v>12</v>
+        <v>1.9</v>
       </c>
       <c r="G327">
-        <v>301</v>
+        <v>327</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
-        <v>633</v>
+        <v>810</v>
       </c>
       <c r="B328" t="s">
-        <v>711</v>
-      </c>
-      <c r="C328" t="s">
-        <v>712</v>
-      </c>
-      <c r="D328" t="s">
-        <v>189</v>
+        <v>707</v>
       </c>
       <c r="E328">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="G328">
-        <v>302</v>
+        <v>328</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
-        <v>635</v>
+        <v>612</v>
       </c>
       <c r="B329" t="s">
-        <v>714</v>
-      </c>
-      <c r="C329" t="s">
-        <v>715</v>
+        <v>708</v>
       </c>
       <c r="E329">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="G329">
-        <v>303</v>
+        <v>329</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
-        <v>637</v>
+        <v>811</v>
       </c>
       <c r="B330" t="s">
-        <v>717</v>
+        <v>709</v>
       </c>
       <c r="E330">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G330">
-        <v>304</v>
+        <v>330</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
-        <v>639</v>
+        <v>812</v>
       </c>
       <c r="B331" t="s">
-        <v>719</v>
-      </c>
-      <c r="C331" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="E331">
-        <v>11</v>
+        <v>67</v>
       </c>
       <c r="G331">
-        <v>305</v>
+        <v>331</v>
       </c>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
-        <v>642</v>
+        <v>813</v>
       </c>
       <c r="B332" t="s">
-        <v>722</v>
-      </c>
-      <c r="C332" t="s">
-        <v>723</v>
+        <v>711</v>
       </c>
       <c r="E332">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="G332">
-        <v>306</v>
+        <v>332</v>
       </c>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
-        <v>928</v>
+        <v>814</v>
       </c>
       <c r="B333" t="s">
-        <v>725</v>
+        <v>712</v>
       </c>
       <c r="E333">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="G333">
-        <v>307</v>
+        <v>333</v>
       </c>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
-        <v>950</v>
+        <v>617</v>
       </c>
       <c r="B334" t="s">
-        <v>727</v>
+        <v>713</v>
       </c>
       <c r="E334">
-        <v>15</v>
+        <v>85</v>
       </c>
       <c r="G334">
-        <v>308</v>
+        <v>333</v>
       </c>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
-        <v>951</v>
+        <v>815</v>
       </c>
       <c r="B335" t="s">
-        <v>729</v>
+        <v>714</v>
       </c>
       <c r="E335">
-        <v>19.899999999999999</v>
+        <v>27</v>
       </c>
       <c r="G335">
-        <v>309</v>
+        <v>334</v>
       </c>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
-        <v>952</v>
+        <v>816</v>
       </c>
       <c r="B336" t="s">
-        <v>731</v>
+        <v>715</v>
       </c>
       <c r="E336">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="G336">
-        <v>310</v>
+        <v>335</v>
       </c>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
-        <v>953</v>
+        <v>817</v>
       </c>
       <c r="B337" t="s">
-        <v>733</v>
+        <v>716</v>
       </c>
       <c r="E337">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G337">
-        <v>311</v>
+        <v>336</v>
       </c>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
-        <v>954</v>
+        <v>619</v>
       </c>
       <c r="B338" t="s">
-        <v>734</v>
-      </c>
-      <c r="C338" t="s">
-        <v>735</v>
+        <v>717</v>
       </c>
       <c r="E338">
-        <v>26.5</v>
+        <v>15</v>
       </c>
       <c r="G338">
-        <v>312</v>
+        <v>337</v>
       </c>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
-        <v>955</v>
+        <v>621</v>
       </c>
       <c r="B339" t="s">
-        <v>737</v>
+        <v>718</v>
       </c>
       <c r="E339">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="G339">
-        <v>313</v>
+        <v>338</v>
       </c>
     </row>
     <row r="340" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
-        <v>915</v>
+        <v>624</v>
       </c>
       <c r="B340" t="s">
-        <v>738</v>
+        <v>719</v>
       </c>
       <c r="E340">
-        <v>157</v>
+        <v>21</v>
       </c>
       <c r="G340">
-        <v>314</v>
+        <v>339</v>
       </c>
     </row>
     <row r="341" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
-        <v>956</v>
+        <v>626</v>
       </c>
       <c r="B341" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="E341">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G341">
-        <v>315</v>
+        <v>340</v>
       </c>
     </row>
     <row r="342" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A342" t="s">
-        <v>957</v>
+        <v>628</v>
       </c>
       <c r="B342" t="s">
-        <v>742</v>
+        <v>721</v>
       </c>
       <c r="E342">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="G342">
-        <v>316</v>
+        <v>341</v>
       </c>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
-        <v>958</v>
+        <v>631</v>
       </c>
       <c r="B343" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
       <c r="E343">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="G343">
-        <v>317</v>
+        <v>342</v>
       </c>
     </row>
     <row r="344" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
-        <v>654</v>
+        <v>633</v>
       </c>
       <c r="B344" t="s">
-        <v>746</v>
+        <v>723</v>
       </c>
       <c r="E344">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="G344">
-        <v>318</v>
+        <v>343</v>
       </c>
     </row>
     <row r="345" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
-        <v>871</v>
+        <v>635</v>
       </c>
       <c r="B345" t="s">
-        <v>748</v>
+        <v>724</v>
       </c>
       <c r="E345">
-        <v>465</v>
+        <v>19.899999999999999</v>
       </c>
       <c r="G345">
-        <v>319</v>
+        <v>344</v>
       </c>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
-        <v>872</v>
+        <v>637</v>
       </c>
       <c r="B346" t="s">
-        <v>749</v>
+        <v>725</v>
       </c>
       <c r="E346">
-        <v>705</v>
+        <v>25</v>
       </c>
       <c r="G346">
-        <v>320</v>
+        <v>345</v>
       </c>
     </row>
     <row r="347" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="B347" t="s">
-        <v>750</v>
+        <v>726</v>
       </c>
       <c r="E347">
-        <v>109</v>
+        <v>42</v>
       </c>
       <c r="G347">
-        <v>321</v>
+        <v>346</v>
       </c>
     </row>
     <row r="348" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
-        <v>873</v>
+        <v>643</v>
       </c>
       <c r="B348" t="s">
-        <v>751</v>
+        <v>727</v>
       </c>
       <c r="E348">
-        <v>145</v>
+        <v>47</v>
       </c>
       <c r="G348">
-        <v>322</v>
+        <v>347</v>
       </c>
     </row>
     <row r="349" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
-        <v>874</v>
+        <v>646</v>
       </c>
       <c r="B349" t="s">
-        <v>752</v>
+        <v>728</v>
       </c>
       <c r="E349">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="G349">
-        <v>323</v>
+        <v>348</v>
       </c>
     </row>
     <row r="350" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
-        <v>875</v>
+        <v>649</v>
       </c>
       <c r="B350" t="s">
-        <v>753</v>
+        <v>729</v>
       </c>
       <c r="E350">
-        <v>38</v>
+        <v>97</v>
       </c>
       <c r="G350">
-        <v>324</v>
+        <v>349</v>
       </c>
     </row>
     <row r="351" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
-        <v>876</v>
+        <v>652</v>
       </c>
       <c r="B351" t="s">
-        <v>754</v>
+        <v>730</v>
       </c>
       <c r="E351">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="G351">
-        <v>325</v>
+        <v>350</v>
       </c>
     </row>
     <row r="352" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="B352" t="s">
-        <v>755</v>
+        <v>731</v>
       </c>
       <c r="E352">
-        <v>99</v>
+        <v>129.9</v>
       </c>
       <c r="G352">
-        <v>326</v>
+        <v>351</v>
       </c>
     </row>
     <row r="353" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
-        <v>877</v>
+        <v>657</v>
       </c>
       <c r="B353" t="s">
-        <v>756</v>
+        <v>732</v>
       </c>
       <c r="E353">
-        <v>1.9</v>
+        <v>222</v>
       </c>
       <c r="G353">
-        <v>327</v>
+        <v>352</v>
       </c>
     </row>
     <row r="354" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
-        <v>878</v>
+        <v>660</v>
       </c>
       <c r="B354" t="s">
-        <v>757</v>
+        <v>733</v>
       </c>
       <c r="E354">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G354">
-        <v>328</v>
+        <v>353</v>
       </c>
     </row>
     <row r="355" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B355" t="s">
-        <v>758</v>
+        <v>734</v>
       </c>
       <c r="E355">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="G355">
-        <v>329</v>
+        <v>354</v>
       </c>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
-        <v>879</v>
+        <v>666</v>
       </c>
       <c r="B356" t="s">
-        <v>759</v>
+        <v>735</v>
       </c>
       <c r="E356">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G356">
-        <v>330</v>
+        <v>355</v>
       </c>
     </row>
     <row r="357" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
-        <v>880</v>
+        <v>668</v>
       </c>
       <c r="B357" t="s">
-        <v>760</v>
+        <v>736</v>
       </c>
       <c r="E357">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="G357">
-        <v>331</v>
+        <v>356</v>
       </c>
     </row>
     <row r="358" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
-        <v>881</v>
+        <v>671</v>
       </c>
       <c r="B358" t="s">
-        <v>761</v>
+        <v>737</v>
       </c>
       <c r="E358">
-        <v>95</v>
+        <v>35</v>
       </c>
       <c r="G358">
-        <v>332</v>
+        <v>357</v>
       </c>
     </row>
     <row r="359" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
-        <v>882</v>
+        <v>674</v>
       </c>
       <c r="B359" t="s">
-        <v>762</v>
+        <v>738</v>
       </c>
       <c r="E359">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="G359">
-        <v>333</v>
+        <v>358</v>
       </c>
     </row>
     <row r="360" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
-        <v>667</v>
+        <v>676</v>
       </c>
       <c r="B360" t="s">
-        <v>763</v>
+        <v>739</v>
       </c>
       <c r="E360">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="G360">
-        <v>333</v>
+        <v>359</v>
       </c>
     </row>
     <row r="361" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
-        <v>883</v>
+        <v>678</v>
       </c>
       <c r="B361" t="s">
-        <v>764</v>
+        <v>740</v>
       </c>
       <c r="E361">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="G361">
-        <v>334</v>
+        <v>360</v>
       </c>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
-        <v>884</v>
+        <v>680</v>
       </c>
       <c r="B362" t="s">
-        <v>765</v>
+        <v>741</v>
       </c>
       <c r="E362">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="G362">
-        <v>335</v>
+        <v>361</v>
       </c>
     </row>
     <row r="363" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
-        <v>885</v>
+        <v>682</v>
       </c>
       <c r="B363" t="s">
-        <v>766</v>
+        <v>742</v>
       </c>
       <c r="E363">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G363">
-        <v>336</v>
+        <v>362</v>
       </c>
     </row>
     <row r="364" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
-        <v>669</v>
+        <v>686</v>
       </c>
       <c r="B364" t="s">
-        <v>767</v>
+        <v>743</v>
       </c>
       <c r="E364">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="G364">
-        <v>337</v>
+        <v>363</v>
       </c>
     </row>
     <row r="365" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
-        <v>671</v>
+        <v>818</v>
       </c>
       <c r="B365" t="s">
-        <v>768</v>
+        <v>744</v>
       </c>
       <c r="E365">
-        <v>17</v>
+        <v>59.9</v>
       </c>
       <c r="G365">
-        <v>338</v>
+        <v>364</v>
       </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
-        <v>674</v>
+        <v>689</v>
       </c>
       <c r="B366" t="s">
-        <v>769</v>
+        <v>745</v>
+      </c>
+      <c r="C366" t="s">
+        <v>746</v>
       </c>
       <c r="E366">
-        <v>21</v>
+        <v>29.9</v>
       </c>
       <c r="G366">
-        <v>339</v>
+        <v>365</v>
       </c>
     </row>
     <row r="367" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A367" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="B367" t="s">
-        <v>770</v>
+        <v>747</v>
+      </c>
+      <c r="C367" t="s">
+        <v>748</v>
       </c>
       <c r="E367">
-        <v>50</v>
+        <v>39.9</v>
       </c>
       <c r="G367">
-        <v>340</v>
+        <v>366</v>
       </c>
     </row>
     <row r="368" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A368" t="s">
-        <v>678</v>
+        <v>693</v>
       </c>
       <c r="B368" t="s">
-        <v>771</v>
+        <v>749</v>
+      </c>
+      <c r="C368" t="s">
+        <v>750</v>
       </c>
       <c r="E368">
-        <v>14.9</v>
+        <v>26</v>
       </c>
       <c r="G368">
-        <v>341</v>
+        <v>367</v>
       </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
-        <v>681</v>
+        <v>695</v>
       </c>
       <c r="B369" t="s">
-        <v>772</v>
+        <v>751</v>
+      </c>
+      <c r="C369" t="s">
+        <v>750</v>
       </c>
       <c r="E369">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G369">
-        <v>342</v>
+        <v>368</v>
       </c>
     </row>
     <row r="370" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
-        <v>683</v>
+        <v>697</v>
       </c>
       <c r="B370" t="s">
-        <v>773</v>
+        <v>752</v>
+      </c>
+      <c r="C370" t="s">
+        <v>753</v>
       </c>
       <c r="E370">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G370">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A371" t="s">
-        <v>685</v>
-      </c>
-      <c r="B371" t="s">
-        <v>774</v>
-      </c>
-      <c r="E371">
-        <v>19.899999999999999</v>
-      </c>
-      <c r="G371">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A372" t="s">
-        <v>687</v>
-      </c>
-      <c r="B372" t="s">
-        <v>775</v>
-      </c>
-      <c r="E372">
-        <v>25</v>
-      </c>
-      <c r="G372">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A373" t="s">
-        <v>690</v>
-      </c>
-      <c r="B373" t="s">
-        <v>776</v>
-      </c>
-      <c r="E373">
-        <v>42</v>
-      </c>
-      <c r="G373">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A374" t="s">
-        <v>693</v>
-      </c>
-      <c r="B374" t="s">
-        <v>777</v>
-      </c>
-      <c r="E374">
-        <v>47</v>
-      </c>
-      <c r="G374">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A375" t="s">
-        <v>696</v>
-      </c>
-      <c r="B375" t="s">
-        <v>778</v>
-      </c>
-      <c r="E375">
-        <v>77</v>
-      </c>
-      <c r="G375">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A376" t="s">
-        <v>699</v>
-      </c>
-      <c r="B376" t="s">
-        <v>779</v>
-      </c>
-      <c r="E376">
-        <v>97</v>
-      </c>
-      <c r="G376">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A377" t="s">
-        <v>702</v>
-      </c>
-      <c r="B377" t="s">
-        <v>780</v>
-      </c>
-      <c r="E377">
-        <v>128</v>
-      </c>
-      <c r="G377">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A378" t="s">
-        <v>704</v>
-      </c>
-      <c r="B378" t="s">
-        <v>781</v>
-      </c>
-      <c r="E378">
-        <v>123.6</v>
-      </c>
-      <c r="G378">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A379" t="s">
-        <v>707</v>
-      </c>
-      <c r="B379" t="s">
-        <v>782</v>
-      </c>
-      <c r="E379">
-        <v>222</v>
-      </c>
-      <c r="G379">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A380" t="s">
-        <v>710</v>
-      </c>
-      <c r="B380" t="s">
-        <v>783</v>
-      </c>
-      <c r="E380">
-        <v>17</v>
-      </c>
-      <c r="G380">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A381" t="s">
-        <v>713</v>
-      </c>
-      <c r="B381" t="s">
-        <v>784</v>
-      </c>
-      <c r="E381">
-        <v>13</v>
-      </c>
-      <c r="G381">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A382" t="s">
-        <v>716</v>
-      </c>
-      <c r="B382" t="s">
-        <v>785</v>
-      </c>
-      <c r="E382">
-        <v>4</v>
-      </c>
-      <c r="G382">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A383" t="s">
-        <v>718</v>
-      </c>
-      <c r="B383" t="s">
-        <v>786</v>
-      </c>
-      <c r="E383">
-        <v>28</v>
-      </c>
-      <c r="G383">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A384" t="s">
-        <v>721</v>
-      </c>
-      <c r="B384" t="s">
-        <v>787</v>
-      </c>
-      <c r="E384">
-        <v>35</v>
-      </c>
-      <c r="G384">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A385" t="s">
-        <v>724</v>
-      </c>
-      <c r="B385" t="s">
-        <v>788</v>
-      </c>
-      <c r="E385">
-        <v>23</v>
-      </c>
-      <c r="G385">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A386" t="s">
-        <v>726</v>
-      </c>
-      <c r="B386" t="s">
-        <v>789</v>
-      </c>
-      <c r="E386">
-        <v>45</v>
-      </c>
-      <c r="G386">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A387" t="s">
-        <v>728</v>
-      </c>
-      <c r="B387" t="s">
-        <v>790</v>
-      </c>
-      <c r="E387">
-        <v>19</v>
-      </c>
-      <c r="G387">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A388" t="s">
-        <v>730</v>
-      </c>
-      <c r="B388" t="s">
-        <v>791</v>
-      </c>
-      <c r="E388">
-        <v>32</v>
-      </c>
-      <c r="G388">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A389" t="s">
-        <v>732</v>
-      </c>
-      <c r="B389" t="s">
-        <v>792</v>
-      </c>
-      <c r="E389">
-        <v>19</v>
-      </c>
-      <c r="G389">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A390" t="s">
-        <v>736</v>
-      </c>
-      <c r="B390" t="s">
-        <v>793</v>
-      </c>
-      <c r="E390">
-        <v>37</v>
-      </c>
-      <c r="G390">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A391" t="s">
-        <v>886</v>
-      </c>
-      <c r="B391" t="s">
-        <v>794</v>
-      </c>
-      <c r="E391">
-        <v>59.9</v>
-      </c>
-      <c r="G391">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A392" t="s">
-        <v>739</v>
-      </c>
-      <c r="B392" t="s">
-        <v>795</v>
-      </c>
-      <c r="C392" t="s">
-        <v>796</v>
-      </c>
-      <c r="E392">
-        <v>29.9</v>
-      </c>
-      <c r="G392">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A393" t="s">
-        <v>741</v>
-      </c>
-      <c r="B393" t="s">
-        <v>797</v>
-      </c>
-      <c r="C393" t="s">
-        <v>798</v>
-      </c>
-      <c r="E393">
-        <v>39.9</v>
-      </c>
-      <c r="G393">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A394" t="s">
-        <v>743</v>
-      </c>
-      <c r="B394" t="s">
-        <v>799</v>
-      </c>
-      <c r="C394" t="s">
-        <v>800</v>
-      </c>
-      <c r="E394">
-        <v>26</v>
-      </c>
-      <c r="G394">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A395" t="s">
-        <v>745</v>
-      </c>
-      <c r="B395" t="s">
-        <v>801</v>
-      </c>
-      <c r="C395" t="s">
-        <v>800</v>
-      </c>
-      <c r="E395">
-        <v>35</v>
-      </c>
-      <c r="G395">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A396" t="s">
-        <v>747</v>
-      </c>
-      <c r="B396" t="s">
-        <v>802</v>
-      </c>
-      <c r="C396" t="s">
-        <v>803</v>
-      </c>
-      <c r="E396">
-        <v>22</v>
-      </c>
-      <c r="G396">
         <v>369</v>
       </c>
     </row>
